--- a/download/ricerca-mondiale-mediazione-tabelle.xlsx
+++ b/download/ricerca-mondiale-mediazione-tabelle.xlsx
@@ -10,11 +10,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Mediazioni per Paese" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Mediatori e registri" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Mediatori Europa 2019-2021" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legenda e fonti" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-Mediatori extra-UE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legenda e fonti" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Mediazioni per Paese'!$A$1:$D$196</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2-Mediatori e registri'!$A$1:$E$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4-Mediatori extra-UE'!$A$1:$F$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4893,12 +4895,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>114 (2025); 1 mediatore ogni 24.474 ab.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://dhkn.gov.al/en/</t>
         </is>
       </c>
     </row>
@@ -4920,12 +4922,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>oltre 2.000 (mediatori giudiziari) (2024); 1 mediatore ogni 22.310 ab.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.mjustice.dz/</t>
         </is>
       </c>
     </row>
@@ -5028,12 +5030,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 17.000 (iscritti MoJ) (2020); 1 mediatore ogni 2.079 ab.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.moj.gov.sa/</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5057,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>4.513 (dato ufficiale 2008) (2008); 1 mediatore ogni 10.151 ab.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://servicios.infoleg.gob.ar/infolegInternet/anexos/55000-59999/59525/norma.htm</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5084,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>~123 (2025)</t>
+          <t>123 (2024); 1 mediatore ogni 22.683 ab.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — profilo paese</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.moj.am/page/582</t>
         </is>
       </c>
     </row>
@@ -5109,12 +5111,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 4.000 (2024); 1 mediatore ogni 6.422 ab.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://msb.org.au/resources/faqs</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5165,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>381 (2024); 1 mediatore ogni 26.614 ab.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://mediasiya.gov.az/</t>
         </is>
       </c>
     </row>
@@ -5217,12 +5219,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>21 (BCC) (2024); 1 mediatore ogni 83.333 ab.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.alayam.com/alayam/economic/1035195/News.html</t>
         </is>
       </c>
     </row>
@@ -5325,12 +5327,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19 (mediatori giudiziari) (2025)</t>
+          <t>19 (2023); 1 mediatore ogni 21.053 ab.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Senior Courts Rules 2025</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.belizejudiciary.org/court-connected-mediators/</t>
         </is>
       </c>
     </row>
@@ -5406,12 +5408,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 1.330 (2025); 1 mediatore ogni 7.023 ab.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://minjust.gov.by/directions/advocacy/mediation/list_register/</t>
         </is>
       </c>
     </row>
@@ -5460,12 +5462,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>oltre 160 (2024); 1 mediatore ogni 20.375 ab.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.umbih.ba/index.php/medijacija/lista-medijatora</t>
         </is>
       </c>
     </row>
@@ -5514,12 +5516,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 1.747 (dato parziale 2017) (2017); 1 mediatore ogni 122.496 ab. [dato parziale/sub-nazionale]</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://conciliajud.cnj.jus.br/ccmj</t>
         </is>
       </c>
     </row>
@@ -5649,12 +5651,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>16 (commerciali) (2022); 1 mediatore ogni 1.045.000 ab.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://ncac.org.kh/en/services/mediation/list-of-mediators/</t>
         </is>
       </c>
     </row>
@@ -5703,12 +5705,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>oltre 2.400 (mediatori+arbitri) (2025); 1 mediatore ogni 15.938 ab.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://mediators.ca/our-adr-partners</t>
         </is>
       </c>
     </row>
@@ -5811,12 +5813,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>3.176.000 mediatori popolari (2023); 1 mediatore ogni 445 ab. [mediazione popolare/comunitaria]</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.moj.gov.cn/</t>
         </is>
       </c>
     </row>
@@ -5865,12 +5867,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>3.680–6.743 (2020-2023); 1 mediatore ogni 10.254 ab.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.sicaac.gov.co/</t>
         </is>
       </c>
     </row>
@@ -6081,12 +6083,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>10 (2025); 1 mediatore ogni 1.119.000 ab.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — http://www.cubadebate.cu/noticias/2025/01/16/toman-posesion-arbitros-y-mediadores-de-la-corte-cubana-de-arbitraje-comercial-internacional/</t>
         </is>
       </c>
     </row>
@@ -6135,12 +6137,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>14 (2019); 1 mediatore ogni 5.143 ab.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.eccourts.org/court-connected-mediation</t>
         </is>
       </c>
     </row>
@@ -6162,12 +6164,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>3.525 (2024); 1 mediatore ogni 5.050 ab.</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.funcionjudicial.gob.ec/</t>
         </is>
       </c>
     </row>
@@ -6216,12 +6218,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>210 (2023); 1 mediatore ogni 30.905 ab.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.pgr.gob.sv/procuraduria-especializada-de-mediacion-y-conciliacion/</t>
         </is>
       </c>
     </row>
@@ -6378,12 +6380,12 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>14 (2016); 1 mediatore ogni 64.286 ab.</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://fijimediation.org/</t>
         </is>
       </c>
     </row>
@@ -6540,12 +6542,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 170 (2023); 1 mediatore ogni 21.824 ab.</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://mediators.ge/</t>
         </is>
       </c>
     </row>
@@ -6594,12 +6596,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>635 (2021); 1 mediatore ogni 48.929 ab.</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://mofep.gov.gh/</t>
         </is>
       </c>
     </row>
@@ -6621,12 +6623,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>76 (2013); 1 mediatore ogni 37.237 ab.</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.disputeresolutionfoundation.org/</t>
         </is>
       </c>
     </row>
@@ -6999,12 +7001,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>16.565 (formati) (2021-2022); 1 mediatore ogni 84.093 ab.</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://mcpc.nic.in/</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7217,12 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 300 (lista giudiziaria) (2024); 1 mediatore ogni 31.500 ab.</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.gov.il/he/pages/mediation_department</t>
         </is>
       </c>
     </row>
@@ -7269,12 +7271,12 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>~371 professionali (+ ~4.465 non professionali) (2024)</t>
+          <t>371 professionali (+4.465 comunitari) (2023); 1 mediatore ogni 51.213 ab.</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — profilo paese</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://mediator.kz/reestr</t>
         </is>
       </c>
     </row>
@@ -7296,12 +7298,12 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 900 attivi (2023-2025); 1 mediatore ogni 58.900 ab.</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://judiciary.go.ke/list-of-accredited-mediators/</t>
         </is>
       </c>
     </row>
@@ -7323,12 +7325,12 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>271 (2022); 1 mediatore ogni 24.686 ab.</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://mediator.kg/mediators/</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7379,12 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>189 (2017); 1 mediatore ogni 9.471 ab.</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://ndermjetesimi.com/en/historiku/</t>
         </is>
       </c>
     </row>
@@ -7944,12 +7946,12 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>977 (2025); 1 mediatore ogni 2.682 ab.</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://mediere.gov.md/sites/default/files/document/attachments/registrul_atestatelor_mediatorilor_2.pdf</t>
         </is>
       </c>
     </row>
@@ -7998,12 +8000,12 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 400 (2023); 1 mediatore ogni 8.375 ab.</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.judcouncil.mn/</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8027,12 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>234 (2023); 1 mediatore ogni 2.650 ab.</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.cazrs.me/</t>
         </is>
       </c>
     </row>
@@ -8268,12 +8270,12 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>~550 (2019-2020)</t>
+          <t>circa 65 (mediazione familiare) (2016); 1 mediatore ogni 83.231 ab.</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.bufdir.no/</t>
         </is>
       </c>
     </row>
@@ -8511,12 +8513,12 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>59 (2024); 1 mediatore ogni 113.559 ab.</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.pj.gov.py/contenido/150-direccion-de-mediacion/1198</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8864,12 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 30.000 Abunzi (2023); 1 mediatore ogni 449 ab. [mediazione popolare/comunitaria]</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://weinsteininternational.org/</t>
         </is>
       </c>
     </row>
@@ -9020,12 +9022,12 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 41 (2017); 1 mediatore ogni 4.390 ab.</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.loc.gov/item/global-legal-monitor/2017-06-12/saint-lucia-awareness-campaign-on-mediation-launched/</t>
         </is>
       </c>
     </row>
@@ -9047,12 +9049,12 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>29 (CAMC Dakar) (2026); 1 mediatore ogni 582.069 ab.</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://arbitrage-senegal.com/liste-des-mediateurs/</t>
         </is>
       </c>
     </row>
@@ -9074,12 +9076,12 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>oltre 1.100 (2019); 1 mediatore ogni 6.209 ab.</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://mpravde.gov.rs/registar-posrednika</t>
         </is>
       </c>
     </row>
@@ -9155,12 +9157,12 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>oltre 500 (SIMI) (2024); 1 mediatore ogni 10.900 ab.</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.simi.org.sg/</t>
         </is>
       </c>
     </row>
@@ -9290,12 +9292,12 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>~8.600 (2019-2020)</t>
+          <t>oltre 8.600 (2024); 1 mediatore ogni 2.577 ab. [mediazione popolare/comunitaria]</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://mediation.gov.lk/en/</t>
         </is>
       </c>
     </row>
@@ -9344,12 +9346,12 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>5.674 (solo Florida) (2024); 1 mediatore ogni 3.839 ab. [dato parziale/sub-nazionale]</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.flcourts.gov/Resources-Services/Alternative-Dispute-Resolution/</t>
         </is>
       </c>
     </row>
@@ -9506,12 +9508,12 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>~800 (2019-2020)</t>
+          <t>oltre 1.500 (FSM); ~200 SKWM (2024); 1 mediatore ogni 5.800 ab.</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.mediation-ch.org/</t>
         </is>
       </c>
     </row>
@@ -9560,12 +9562,12 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 4.054 (conciliatori township) (2022); 1 mediatore ogni 5.814 ab. [mediazione popolare/comunitaria]</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://data.gov.tw/dataset/13947</t>
         </is>
       </c>
     </row>
@@ -9776,12 +9778,12 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 45.154 (2024); 1 mediatore ogni 1.878 ab.</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://adb.adalet.gov.tr/</t>
         </is>
       </c>
     </row>
@@ -9857,12 +9859,12 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 160 (NAMU) (2024); 1 mediatore ogni 273.688 ab.</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — http://namu.com.ua/ua/members/</t>
         </is>
       </c>
     </row>
@@ -9884,12 +9886,12 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>71 (2024); 1 mediatore ogni 645.775 ab.</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://judiciary.go.ug/</t>
         </is>
       </c>
     </row>
@@ -9938,12 +9940,12 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>N/D (20 cariche nei centri PJ) (N/D)</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.poderjudicial.gub.uy/institucional/centros-de-mediacion.html</t>
         </is>
       </c>
     </row>
@@ -9965,12 +9967,12 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 1.900 (+3.000 formati) (2025); 1 mediatore ogni 18.379 ab.</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.adliya.uz/</t>
         </is>
       </c>
     </row>
@@ -10073,12 +10075,12 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>190 (2023); 1 mediatore ogni 102.474 ab.</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://judiciaryzambia.com/mediation-in-zambia-and-statistics/</t>
         </is>
       </c>
     </row>
@@ -11359,7 +11361,7 @@
     <row r="33" ht="60" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Fonte: Avv. Carlo Alberto Calcagno, «Mediatori in Europa 2019-2021», elaborazione su registri europei nazionali disponibili. Il 2021 non è disponibile per Inghilterra e Galles, Irlanda del Nord e Scozia (serie ferma al 2020). Totale UE/UK mediatori: 83.213 (2019) → 79.598 (2020) → 76.085 (2021).</t>
+          <t>Fonte: Avv. Carlo Alberto Calcagno, «Mediatori in Europa 2019-2021», elaborazione su registri europei nazionali disponibili. Il 2021 non è disponibile per Inghilterra e Galles, Irlanda del Nord e Scozia. Totale UE/UK: 83.213 (2019) → 79.598 (2020) → 76.085 (2021).</t>
         </is>
       </c>
     </row>
@@ -11377,6 +11379,1639 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Paese</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>N. mediatori</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Anno</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>1 mediatore ogni (ab.)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Fonte (registro ufficiale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Albania</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>24.474</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://dhkn.gov.al/en/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>oltre 2.000 (mediatori giudiziari)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>22.310</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mjustice.dz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Arabia Saudita</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>circa 17.000 (iscritti MoJ)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2.079</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moj.gov.sa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>4.513 (dato ufficiale 2008)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10.151</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/55000-59999/59525/norma.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22.683</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moj.am/page/582</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>circa 4.000</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6.422</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>https://msb.org.au/resources/faqs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Azerbaigian</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>26.614</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://mediasiya.gov.az/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>21 (BCC)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>83.333</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.alayam.com/alayam/economic/1035195/News.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Belize</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21.053</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.belizejudiciary.org/court-connected-mediators/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Bielorussia</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>circa 1.330</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7.023</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>https://minjust.gov.by/directions/advocacy/mediation/list_register/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia ed Erzegovina</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>oltre 160</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20.375</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.umbih.ba/index.php/medijacija/lista-medijatora</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Brasile</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>circa 1.747 (dato parziale 2017)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>122.496</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>dato sub-nazionale/parziale</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>https://conciliajud.cnj.jus.br/ccmj</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Cambogia</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>16 (commerciali)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1.045.000</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>https://ncac.org.kh/en/services/mediation/list-of-mediators/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>oltre 2.400 (mediatori+arbitri)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>15.938</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>https://mediators.ca/our-adr-partners</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Cina</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>3.176.000 mediatori popolari</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>mediazione popolare/comunitaria</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moj.gov.cn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>3.680–6.743</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2020-2023</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10.254</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sicaac.gov.co/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Cuba</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1.119.000</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cubadebate.cu/noticias/2025/01/16/toman-posesion-arbitros-y-mediadores-de-la-corte-cubana-de-arbitraje-comercial-internacional/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Dominica</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5.143</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.eccourts.org/court-connected-mediation</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>3.525</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5.050</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.funcionjudicial.gob.ec/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>30.905</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pgr.gob.sv/procuraduria-especializada-de-mediacion-y-conciliacion/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Figi</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>64.286</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>https://fijimediation.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>circa 170</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>21.824</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>https://mediators.ge/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>48.929</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>https://mofep.gov.gh/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Giamaica</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>37.237</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.disputeresolutionfoundation.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>16.565 (formati)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2021-2022</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>84.093</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>https://mcpc.nic.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Israele</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>circa 300 (lista giudiziaria)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>31.500</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.il/he/pages/mediation_department</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Kazakistan</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>371 professionali (+4.465 comunitari)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>51.213</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>https://mediator.kz/reestr</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>circa 900 attivi</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>2023-2025</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>58.900</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>https://judiciary.go.ke/list-of-accredited-mediators/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Kirghizistan</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>24.686</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>https://mediator.kg/mediators/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>9.471</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>https://ndermjetesimi.com/en/historiku/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Moldova</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>2.682</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>https://mediere.gov.md/sites/default/files/document/attachments/registrul_atestatelor_mediatorilor_2.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Mongolia</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>circa 400</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>8.375</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.judcouncil.mn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>2.650</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cazrs.me/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Norvegia</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>circa 65 (mediazione familiare)</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>83.231</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bufdir.no/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>113.559</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pj.gov.py/contenido/150-direccion-de-mediacion/1198</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Ruanda</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>circa 30.000 Abunzi</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>mediazione popolare/comunitaria</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>https://weinsteininternational.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Santa Lucia</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>circa 41</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>4.390</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.loc.gov/item/global-legal-monitor/2017-06-12/saint-lucia-awareness-campaign-on-mediation-launched/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>29 (CAMC Dakar)</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>582.069</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>https://arbitrage-senegal.com/liste-des-mediateurs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>oltre 1.100</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>6.209</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>https://mpravde.gov.rs/registar-posrednika</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>oltre 500 (SIMI)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10.900</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.simi.org.sg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>oltre 8.600</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>2.577</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>mediazione popolare/comunitaria</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>https://mediation.gov.lk/en/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Stati Uniti (Florida)</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>5.674 (solo Florida)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>3.839</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>dato sub-nazionale/parziale</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flcourts.gov/Resources-Services/Alternative-Dispute-Resolution/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Svizzera</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>oltre 1.500 (FSM); ~200 SKWM</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>5.800</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mediation-ch.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>circa 4.054 (conciliatori township)</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>5.814</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>mediazione popolare/comunitaria</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>https://data.gov.tw/dataset/13947</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Turchia</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>circa 45.154</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>1.878</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>https://adb.adalet.gov.tr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Ucraina</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>circa 160 (NAMU)</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>273.688</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>http://namu.com.ua/ua/members/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>645.775</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>https://judiciary.go.ug/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>circa 1.900 (+3.000 formati)</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>18.379</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adliya.uz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Zambia</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>102.474</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>https://judiciaryzambia.com/mediation-in-zambia-and-statistics/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="72" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Conteggio «registro per registro» dei mediatori fuori dall'UE/UK, consultando ciascun registro ufficiale nazionale nella lingua ufficiale del luogo (ricerca luglio 2026). La densità è calcolata sulla popolazione nazionale. Le categorie «mediazione popolare/comunitaria» (Cina, Ruanda, Sri Lanka, Taiwan) e «dato sub-nazionale/parziale» (USA-Florida, Brasile) NON sono omogenee con i registri professionali e non vanno sommate. Per i Paesi non elencati non risulta pubblicato un conteggio ufficiale: N/D.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F50"/>
+  <mergeCells count="1">
+    <mergeCell ref="A51:F51"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -11400,79 +13035,79 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Elaborazione dell'autore sui registri europei nazionali: numero di mediatori 2019/2020/2021, popolazione e rapporto mediatori/abitanti per 30 giurisdizioni UE+UK (foglio «3-Mediatori Europa 2019-2021»). Totale UE/UK: 83.213 (2019), 79.598 (2020), 76.085 (2021). FONTE PRINCIPALE per il numero dei mediatori.</t>
+          <t>Elaborazione dell'autore sui registri europei nazionali: mediatori 2019/2020/2021, popolazione e densità per 30 giurisdizioni UE+UK (foglio 3). Totale UE/UK: 83.213 (2019), 79.598 (2020), 76.085 (2021). FONTE PRINCIPALE per il numero dei mediatori UE.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>CEPEJ — Evaluation Report 2024 (dati 2022)</t>
+          <t>Registri ufficiali nazionali extra-UE (ricerca in lingua locale)</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Pubbl. 16 ott 2024, 44+2 Stati. Mediana 17 mediatori accreditati/100.000 ab. (2021; 9,5 nel 2012). Mediazione di corte in tutti gli Stati, obbligatoria in metà, ma sottoutilizzata. Banca dati CEPEJ-STAT per i dati per Paese/anno.</t>
+          <t>Conteggio registro per registro dei mediatori fuori dall'UE/UK (luglio 2026): 49 Paesi con conteggio (foglio 4). Per gli altri: N/D.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Commissione europea — EU Justice Scoreboard</t>
+          <t>CEPEJ — Evaluation Report 2024 (dati 2022)</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Promozione ADR, pendenze, alcuni volumi di mediazione (edizione 2026: COM(2026) 273)</t>
+          <t>44+2 Stati. Mediana 17 mediatori accreditati/100.000 ab. (2021). Banca dati CEPEJ-STAT per Paese/anno.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Registri e statistiche ministeriali nazionali</t>
+          <t>Commissione europea — EU Justice Scoreboard</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>es. DGSTAT Italia, CGPJ Spagna, DGPJ Portogallo, PMS Rep. Ceca, ecc.</t>
+          <t>Promozione ADR, pendenze, alcuni volumi di mediazione (ed. 2026: COM(2026) 273).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>mediareinformati.it</t>
+          <t>Registri e statistiche ministeriali nazionali</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Compilazione comparata dei 195 ordinamenti: registri, background dei mediatori, profili paese</t>
+          <t>es. DGSTAT Italia, CGPJ Spagna, DGPJ Portogallo, PMS Rep. Ceca, ecc.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>C.A. Calcagno, «Arbitrato e negoziato in Europa» (Cendon 2020)</t>
+          <t>mediareinformati.it</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Sintesi comparata UE su numero mediatori e mediazioni (Tabelle 11-12)</t>
+          <t>195 profili paese: registri, background, profili.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>UNCITRAL / ICC / centri ADR nazionali</t>
+          <t>C.A. Calcagno, «Arbitrato e negoziato in Europa» (Cendon 2020)</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Cornice normativa e casistica commerciale internazionale (non forniscono conteggi nazionali)</t>
+          <t>Sintesi comparata UE (Tabelle 11-12).</t>
         </is>
       </c>
     </row>
@@ -11488,7 +13123,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>«Best effort», non esaustivo. Per il NUMERO DI MEDIATORI si dispone ora di dati per 30 giurisdizioni europee (UE+UK, 2019-2021, elaborazione C.A. Calcagno); per gli altri Paesi: N/D o stime di profilo. Per il NUMERO DI MEDIAZIONI i conteggi affidabili restano limitati a ~15 Paesi. Definizioni di «mediazione» non uniformi; molti dati riferiti a mediazione familiare/penale o intragiudiziale, non al totale. Anni di riferimento eterogenei.</t>
+          <t>«Best effort», non esaustivo. Mediatori: 30 giurisdizioni UE+UK (2019-2021, C.A. Calcagno) + 49 Paesi extra-UE (2026, registro per registro). Altri Paesi: N/D. Le categorie mediazione popolare/comunitaria (Cina, Ruanda, Sri Lanka, Taiwan) e dato sub-nazionale/parziale (USA-Florida, Brasile) non sono omogenee con i registri professionali e non vanno sommate. Mediazioni: conteggi affidabili ~15 Paesi. Definizioni non uniformi; anni eterogenei.</t>
         </is>
       </c>
     </row>

--- a/download/ricerca-mondiale-mediazione-tabelle.xlsx
+++ b/download/ricerca-mondiale-mediazione-tabelle.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Mediazioni per Paese'!$A$1:$D$196</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2-Mediatori e registri'!$A$1:$E$196</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4-Mediatori extra-UE'!$A$1:$F$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4-Mediatori extra-UE'!$A$1:$F$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4868,12 +4868,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>24 (formati ACDR, non più operativo) (2019); 1 mediatore ogni 1.670.833 ab.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://adrcenter.com/caso-studio/establish-afghanistan-centre-for-alternative-dispute-resolution/</t>
         </is>
       </c>
     </row>
@@ -5354,12 +5354,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>107 (lista CAMeC 2025-2027) (2025); 1 mediatore ogni 116.355 ab.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://camec.bj/</t>
         </is>
       </c>
     </row>
@@ -5381,12 +5381,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 2.870 (formati BNLI, cumulativo) (2022); 1 mediatore ogni 272 ab. [mediazione popolare/comunitaria]</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://bnli.bt/wp-content/uploads/2023/02/CAM-2022.pdf</t>
         </is>
       </c>
     </row>
@@ -5435,12 +5435,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 157 (conciliadores judiciales) (2016); 1 mediatore ogni 75.350 ab.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.conciliacionbolivia.org/mapa-de-la-conciliacion</t>
         </is>
       </c>
     </row>
@@ -5543,12 +5543,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>almeno 10 (BDAC) (2022); 1 mediatore ogni 44.000 ab.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://thebruneian.news/2025/02/23/bdac-brunei-darussalams-centre-for-alternative-dispute-resolution/</t>
         </is>
       </c>
     </row>
@@ -5678,12 +5678,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 20 (CMAG/OHADA) (2019); 1 mediatore ogni 1.360.000 ab.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.ohada.com/actualite/5238/</t>
         </is>
       </c>
     </row>
@@ -5921,12 +5921,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>52 (arbitri+mediatori, dato combinato) (2020) [dato parziale/sub-nazionale]</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — http://unicongo.cg/2021/11/J-ECO-10</t>
         </is>
       </c>
     </row>
@@ -5975,12 +5975,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 5.000 (conciliatori giudiziari) (2023); 1 mediatore ogni 10.348 ab. [mediazione popolare/comunitaria]</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — http://www.cbinews.co.kr/news/articleView.html?idxno=20699</t>
         </is>
       </c>
     </row>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>16-21 (CACI) (2020); 1 mediatore ogni 1.690.625 ab.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://news.abidjan.net/articles/726030</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 80 (panel CRCICA) (2016); 1 mediatore ogni 1.303.750 ab.</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://crcica.org/mediation/panel-of-mediators/</t>
         </is>
       </c>
     </row>
@@ -6245,12 +6245,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>58+ (solo Abu Dhabi ADJD) (2025) [dato parziale/sub-nazionale]</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.adjd.gov.ae/</t>
         </is>
       </c>
     </row>
@@ -6488,12 +6488,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 30 (IIMAC) (2021); 1 mediatore ogni 76.667 ab.</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://gabonactu.com/blog/2023/12/25/dix-mediateurs-daffaires-recoivent-des-certificats-de-liimac/</t>
         </is>
       </c>
     </row>
@@ -6515,12 +6515,12 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 18 (Judiciary CC-ADR) (2023); 1 mediatore ogni 138.333 ab.</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://judiciary.gov.gm/court-connected</t>
         </is>
       </c>
     </row>
@@ -6785,12 +6785,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 100 (Unidad RAC OJ) (2022); 1 mediatore ogni 176.000 ab.</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — http://asies.org.gt/pdf/201310_diagnostico_centros_de_mediacion_rac_daj.pdf</t>
         </is>
       </c>
     </row>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 1.900 (HKMAAL) (2020); 1 mediatore ogni 3.937 ab.</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.hkmaal.org.hk/</t>
         </is>
       </c>
     </row>
@@ -7028,12 +7028,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>oltre 2.000 (dato parziale) (2022) [dato parziale/sub-nazionale]</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.hukumonline.com/berita/a/lt62ff0e1b4d1d1/</t>
         </is>
       </c>
     </row>
@@ -7055,12 +7055,12 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 16.000 (Consigli risoluzione controversie) (2024); 1 mediatore ogni 5.495 ab. [mediazione popolare/comunitaria]</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://mehrnews.com/news/6308238/</t>
         </is>
       </c>
     </row>
@@ -7757,12 +7757,12 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>113 (panel MIMC) (2026); 1 mediatore ogni 297.080 ab.</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.mimc.org.my/list-of-accredited-mediators/</t>
         </is>
       </c>
     </row>
@@ -7919,12 +7919,12 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>649 (solo Città del Messico) (2024) [dato parziale/sub-nazionale]</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.poderjudicialcdmx.gob.mx/cja/mediacion-privada-2/</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 114 (solo centro MICADR) (2026) [dato parziale/sub-nazionale]</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.micadr.com/accredited-mediator-2/</t>
         </is>
       </c>
     </row>
@@ -8540,12 +8540,12 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 58.738 conciliatori extragiudiziali (2020); 1 mediatore ogni 574 ab.</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://laley.pe/art/6527/existen-mas-de-52-mil-conciliadores-extrajudiciales-a-nivel-nacional</t>
         </is>
       </c>
     </row>
@@ -8621,12 +8621,12 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>6 (panel QICDRC) (2026); 1 mediatore ogni 448.333 ab.</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.qicdrc.gov.qa/services/mediation</t>
         </is>
       </c>
     </row>
@@ -8891,12 +8891,12 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>oltre 100 (unica SRO registrata) (2025) [dato parziale/sub-nazionale]</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.all-sro.ru/register/sromed/</t>
         </is>
       </c>
     </row>
@@ -8972,12 +8972,12 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 47 (AMSA) (2017); 1 mediatore ogni 4.681 ab.</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.samoaobserver.ws/en/21_12_2017/local/28089/Twenty-four-Mediators-graduate.htm</t>
         </is>
       </c>
     </row>
@@ -9400,12 +9400,12 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>233 (court-annexed, DOJ) (2015); 1 mediatore ogni 254.893 ab.</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.justice.gov.za/mediation/mediation.html</t>
         </is>
       </c>
     </row>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>7 (Comitato CATO) (2024); 1 mediatore ogni 1.211.429 ab.</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://cato.tg/</t>
         </is>
       </c>
     </row>
@@ -9751,12 +9751,12 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>11 (mediatori bancari) (2024); 1 mediatore ogni 1.114.545 ab.</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.cbf.org.tn/contacts-des-mediateurs-2/</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>3 (Office People's Lawyer) (2023); 1 mediatore ogni 3.667 ab.</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://disputescentre.com.au/mediation-in-the-south-pacific-islands/</t>
         </is>
       </c>
     </row>
@@ -9940,7 +9940,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>N/D (20 cariche nei centri PJ) (N/D)</t>
+          <t>circa 30 (Centri PJ) (2023); 1 mediatore ogni 114.333 ab.</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>343 (mediatori commerciali) (2022); 1 mediatore ogni 284.169 ab.</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://tapchicongthuong.vn/phap-luat-ve-hoa-giai-thuong-mai-tu-thuc-tien-thanh-pho-ho-chi-minh-thuc-trang-va-giai-phap-103581.htm</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -11425,22 +11425,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Albania</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>24 (formati ACDR, non più operativo)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>24.474</t>
+          <t>1.670.833</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -11450,29 +11450,29 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://dhkn.gov.al/en/</t>
+          <t>https://adrcenter.com/caso-studio/establish-afghanistan-centre-for-alternative-dispute-resolution/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Albania</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>oltre 2.000 (mediatori giudiziari)</t>
+          <t>114</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>22.310</t>
+          <t>24.474</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -11482,29 +11482,29 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://www.mjustice.dz/</t>
+          <t>https://dhkn.gov.al/en/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Arabia Saudita</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>circa 17.000 (iscritti MoJ)</t>
+          <t>oltre 2.000 (mediatori giudiziari)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2.079</t>
+          <t>22.310</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -11514,29 +11514,29 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://www.moj.gov.sa/</t>
+          <t>https://www.mjustice.dz/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Arabia Saudita</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>4.513 (dato ufficiale 2008)</t>
+          <t>circa 17.000 (iscritti MoJ)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10.151</t>
+          <t>2.079</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -11546,29 +11546,29 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/55000-59999/59525/norma.htm</t>
+          <t>https://www.moj.gov.sa/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>4.513 (dato ufficiale 2008)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22.683</t>
+          <t>10.151</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -11578,19 +11578,19 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://www.moj.am/page/582</t>
+          <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/55000-59999/59525/norma.htm</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>circa 4.000</t>
+          <t>123</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6.422</t>
+          <t>22.683</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -11610,19 +11610,19 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://msb.org.au/resources/faqs</t>
+          <t>https://www.moj.am/page/582</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Azerbaigian</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>circa 4.000</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>26.614</t>
+          <t>6.422</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -11642,19 +11642,19 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://mediasiya.gov.az/</t>
+          <t>https://msb.org.au/resources/faqs</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Azerbaigian</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>21 (BCC)</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83.333</t>
+          <t>26.614</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -11674,29 +11674,29 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://www.alayam.com/alayam/economic/1035195/News.html</t>
+          <t>https://mediasiya.gov.az/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Belize</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21 (BCC)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21.053</t>
+          <t>83.333</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -11706,29 +11706,29 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://www.belizejudiciary.org/court-connected-mediators/</t>
+          <t>https://www.alayam.com/alayam/economic/1035195/News.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Bielorussia</t>
+          <t>Belize</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>circa 1.330</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7.023</t>
+          <t>21.053</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -11738,29 +11738,29 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>https://minjust.gov.by/directions/advocacy/mediation/list_register/</t>
+          <t>https://www.belizejudiciary.org/court-connected-mediators/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Bosnia ed Erzegovina</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>oltre 160</t>
+          <t>107 (lista CAMeC 2025-2027)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20.375</t>
+          <t>116.355</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -11770,61 +11770,61 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://www.umbih.ba/index.php/medijacija/lista-medijatora</t>
+          <t>https://camec.bj/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Brasile</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>circa 1.747 (dato parziale 2017)</t>
+          <t>circa 2.870 (formati BNLI, cumulativo)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>122.496</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>dato sub-nazionale/parziale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>https://conciliajud.cnj.jus.br/ccmj</t>
+          <t>https://bnli.bt/wp-content/uploads/2023/02/CAM-2022.pdf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Cambogia</t>
+          <t>Bielorussia</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>16 (commerciali)</t>
+          <t>circa 1.330</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1.045.000</t>
+          <t>7.023</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -11834,29 +11834,29 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://ncac.org.kh/en/services/mediation/list-of-mediators/</t>
+          <t>https://minjust.gov.by/directions/advocacy/mediation/list_register/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>oltre 2.400 (mediatori+arbitri)</t>
+          <t>circa 157 (conciliadores judiciales)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15.938</t>
+          <t>75.350</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -11866,93 +11866,93 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>https://mediators.ca/our-adr-partners</t>
+          <t>https://www.conciliacionbolivia.org/mapa-de-la-conciliacion</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Cina</t>
+          <t>Bosnia ed Erzegovina</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>3.176.000 mediatori popolari</t>
+          <t>oltre 160</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>20.375</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://www.moj.gov.cn/</t>
+          <t>https://www.umbih.ba/index.php/medijacija/lista-medijatora</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brasile</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>3.680–6.743</t>
+          <t>circa 1.747 (dato parziale 2017)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2020-2023</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10.254</t>
+          <t>122.496</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>https://www.sicaac.gov.co/</t>
+          <t>https://conciliajud.cnj.jus.br/ccmj</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Brunei</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>almeno 10 (BDAC)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1.119.000</t>
+          <t>44.000</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -11962,29 +11962,29 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>http://www.cubadebate.cu/noticias/2025/01/16/toman-posesion-arbitros-y-mediadores-de-la-corte-cubana-de-arbitraje-comercial-internacional/</t>
+          <t>https://thebruneian.news/2025/02/23/bdac-brunei-darussalams-centre-for-alternative-dispute-resolution/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Dominica</t>
+          <t>Cambogia</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16 (commerciali)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5.143</t>
+          <t>1.045.000</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -11994,29 +11994,29 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>https://www.eccourts.org/court-connected-mediation</t>
+          <t>https://ncac.org.kh/en/services/mediation/list-of-mediators/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Camerun</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>circa 20 (CMAG/OHADA)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5.050</t>
+          <t>1.360.000</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -12026,29 +12026,29 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://www.funcionjudicial.gob.ec/</t>
+          <t>https://www.ohada.com/actualite/5238/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>El Salvador</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>oltre 2.400 (mediatori+arbitri)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30.905</t>
+          <t>15.938</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -12058,61 +12058,61 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>https://www.pgr.gob.sv/procuraduria-especializada-de-mediacion-y-conciliacion/</t>
+          <t>https://mediators.ca/our-adr-partners</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Figi</t>
+          <t>Cina</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3.176.000 mediatori popolari</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>64.286</t>
+          <t>445</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://fijimediation.org/</t>
+          <t>https://www.moj.gov.cn/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>circa 170</t>
+          <t>3.680–6.743</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2020-2023</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>21.824</t>
+          <t>10.254</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -12122,61 +12122,61 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://mediators.ge/</t>
+          <t>https://www.sicaac.gov.co/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Corea del Sud</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>circa 5.000 (conciliatori giudiziari)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>48.929</t>
+          <t>10.348</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>https://mofep.gov.gh/</t>
+          <t>http://www.cbinews.co.kr/news/articleView.html?idxno=20699</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Giamaica</t>
+          <t>Costa d'Avorio</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>16-21 (CACI)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>37.237</t>
+          <t>1.690.625</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -12186,29 +12186,29 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://www.disputeresolutionfoundation.org/</t>
+          <t>https://news.abidjan.net/articles/726030</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>16.565 (formati)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2021-2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>84.093</t>
+          <t>1.119.000</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -12218,29 +12218,29 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://mcpc.nic.in/</t>
+          <t>http://www.cubadebate.cu/noticias/2025/01/16/toman-posesion-arbitros-y-mediadores-de-la-corte-cubana-de-arbitraje-comercial-internacional/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Israele</t>
+          <t>Dominica</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>circa 300 (lista giudiziaria)</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>31.500</t>
+          <t>5.143</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -12250,29 +12250,29 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>https://www.gov.il/he/pages/mediation_department</t>
+          <t>https://www.eccourts.org/court-connected-mediation</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Kazakistan</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>371 professionali (+4.465 comunitari)</t>
+          <t>3.525</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>51.213</t>
+          <t>5.050</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -12282,29 +12282,29 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://mediator.kz/reestr</t>
+          <t>https://www.funcionjudicial.gob.ec/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Egitto</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>circa 900 attivi</t>
+          <t>circa 80 (panel CRCICA)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2023-2025</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>58.900</t>
+          <t>1.303.750</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -12314,29 +12314,29 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>https://judiciary.go.ke/list-of-accredited-mediators/</t>
+          <t>https://crcica.org/mediation/panel-of-mediators/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Kirghizistan</t>
+          <t>El Salvador</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>210</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>24.686</t>
+          <t>30.905</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -12346,29 +12346,29 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://mediator.kg/mediators/</t>
+          <t>https://www.pgr.gob.sv/procuraduria-especializada-de-mediacion-y-conciliacion/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Kosovo</t>
+          <t>Figi</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>9.471</t>
+          <t>64.286</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -12378,29 +12378,29 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://ndermjetesimi.com/en/historiku/</t>
+          <t>https://fijimediation.org/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>circa 30 (IIMAC)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2.682</t>
+          <t>76.667</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -12410,19 +12410,19 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://mediere.gov.md/sites/default/files/document/attachments/registrul_atestatelor_mediatorilor_2.pdf</t>
+          <t>https://gabonactu.com/blog/2023/12/25/dix-mediateurs-daffaires-recoivent-des-certificats-de-liimac/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>circa 400</t>
+          <t>circa 18 (Judiciary CC-ADR)</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>8.375</t>
+          <t>138.333</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -12442,19 +12442,19 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>https://www.judcouncil.mn/</t>
+          <t>https://judiciary.gov.gm/court-connected</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>circa 170</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2.650</t>
+          <t>21.824</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -12474,29 +12474,29 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://www.cazrs.me/</t>
+          <t>https://mediators.ge/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Norvegia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>circa 65 (mediazione familiare)</t>
+          <t>635</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>83.231</t>
+          <t>48.929</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -12506,29 +12506,29 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>https://www.bufdir.no/</t>
+          <t>https://mofep.gov.gh/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Giamaica</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>113.559</t>
+          <t>37.237</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -12538,61 +12538,61 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://www.pj.gov.py/contenido/150-direccion-de-mediacion/1198</t>
+          <t>https://www.disputeresolutionfoundation.org/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Ruanda</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>circa 30.000 Abunzi</t>
+          <t>circa 100 (Unidad RAC OJ)</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>176.000</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>https://weinsteininternational.org/</t>
+          <t>http://asies.org.gt/pdf/201310_diagnostico_centros_de_mediacion_rac_daj.pdf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Santa Lucia</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>circa 41</t>
+          <t>circa 1.900 (HKMAAL)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>4.390</t>
+          <t>3.937</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -12602,29 +12602,29 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/item/global-legal-monitor/2017-06-12/saint-lucia-awareness-campaign-on-mediation-launched/</t>
+          <t>https://www.hkmaal.org.hk/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>29 (CAMC Dakar)</t>
+          <t>16.565 (formati)</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2021-2022</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>582.069</t>
+          <t>84.093</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -12634,51 +12634,51 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>https://arbitrage-senegal.com/liste-des-mediateurs/</t>
+          <t>https://mcpc.nic.in/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>oltre 1.100</t>
+          <t>circa 16.000 (Consigli risoluzione controversie)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>6.209</t>
+          <t>5.495</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://mpravde.gov.rs/registar-posrednika</t>
+          <t>https://mehrnews.com/news/6308238/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Israele</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>oltre 500 (SIMI)</t>
+          <t>circa 300 (lista giudiziaria)</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>10.900</t>
+          <t>31.500</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -12698,93 +12698,93 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>https://www.simi.org.sg/</t>
+          <t>https://www.gov.il/he/pages/mediation_department</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Kazakistan</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>oltre 8.600</t>
+          <t>371 professionali (+4.465 comunitari)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2.577</t>
+          <t>51.213</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://mediation.gov.lk/en/</t>
+          <t>https://mediator.kz/reestr</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Stati Uniti (Florida)</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>5.674 (solo Florida)</t>
+          <t>circa 900 attivi</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023-2025</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3.839</t>
+          <t>58.900</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>dato sub-nazionale/parziale</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>https://www.flcourts.gov/Resources-Services/Alternative-Dispute-Resolution/</t>
+          <t>https://judiciary.go.ke/list-of-accredited-mediators/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Svizzera</t>
+          <t>Kirghizistan</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>oltre 1.500 (FSM); ~200 SKWM</t>
+          <t>271</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>5.800</t>
+          <t>24.686</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -12794,51 +12794,51 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://www.mediation-ch.org/</t>
+          <t>https://mediator.kg/mediators/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Kosovo</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>circa 4.054 (conciliatori township)</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>5.814</t>
+          <t>9.471</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.tw/dataset/13947</t>
+          <t>https://ndermjetesimi.com/en/historiku/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Turchia</t>
+          <t>Macedonia del Nord</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>circa 45.154</t>
+          <t>circa 45 (Camera KMRSM)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1.878</t>
+          <t>46.000</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -12858,29 +12858,29 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>https://adb.adalet.gov.tr/</t>
+          <t>https://www.kmrsm.org.mk/medijatori/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Ucraina</t>
+          <t>Malesia</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>circa 160 (NAMU)</t>
+          <t>113 (panel MIMC)</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>273.688</t>
+          <t>297.080</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -12890,29 +12890,29 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>http://namu.com.ua/ua/members/</t>
+          <t>https://www.mimc.org.my/list-of-accredited-mediators/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>977</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>645.775</t>
+          <t>2.682</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -12922,29 +12922,29 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://judiciary.go.ug/</t>
+          <t>https://mediere.gov.md/sites/default/files/document/attachments/registrul_atestatelor_mediatorilor_2.pdf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>circa 1.900 (+3.000 formati)</t>
+          <t>circa 400</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>18.379</t>
+          <t>8.375</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -12954,53 +12954,853 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>https://www.adliya.uz/</t>
+          <t>https://www.judcouncil.mn/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>2.650</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cazrs.me/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Norvegia</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>circa 65 (mediazione familiare)</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>83.231</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bufdir.no/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>113.559</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pj.gov.py/contenido/150-direccion-de-mediacion/1198</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Perù</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>circa 58.738 conciliatori extragiudiziali</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>https://laley.pe/art/6527/existen-mas-de-52-mil-conciliadores-extrajudiciales-a-nivel-nacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>6 (panel QICDRC)</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>448.333</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qicdrc.gov.qa/services/mediation</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Ruanda</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>circa 30.000 Abunzi</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>mediazione popolare/comunitaria</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>https://weinsteininternational.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Samoa</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>circa 47 (AMSA)</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>4.681</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.samoaobserver.ws/en/21_12_2017/local/28089/Twenty-four-Mediators-graduate.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Santa Lucia</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>circa 41</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>4.390</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.loc.gov/item/global-legal-monitor/2017-06-12/saint-lucia-awareness-campaign-on-mediation-launched/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>29 (CAMC Dakar)</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>582.069</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>https://arbitrage-senegal.com/liste-des-mediateurs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>oltre 1.100</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>6.209</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>https://mpravde.gov.rs/registar-posrednika</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>oltre 500 (SIMI)</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>10.900</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.simi.org.sg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>oltre 8.600</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>2.577</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>mediazione popolare/comunitaria</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>https://mediation.gov.lk/en/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Stati Uniti (Florida)</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>5.674 (solo Florida)</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>3.839</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>dato sub-nazionale/parziale</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flcourts.gov/Resources-Services/Alternative-Dispute-Resolution/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Sudafrica</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>233 (court-annexed, DOJ)</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>254.893</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.za/mediation/mediation.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Svizzera</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>oltre 1.500 (FSM); ~200 SKWM</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>5.800</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mediation-ch.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>circa 4.054 (conciliatori township)</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>5.814</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>mediazione popolare/comunitaria</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>https://data.gov.tw/dataset/13947</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Togo</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>7 (Comitato CATO)</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>1.211.429</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>https://cato.tg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>11 (mediatori bancari)</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>1.114.545</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cbf.org.tn/contacts-des-mediateurs-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Turchia</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>circa 45.154</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>1.878</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>https://adb.adalet.gov.tr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Tuvalu</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>3 (Office People's Lawyer)</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>3.667</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>https://disputescentre.com.au/mediation-in-the-south-pacific-islands/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Ucraina</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>circa 160 (NAMU)</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>273.688</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>http://namu.com.ua/ua/members/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>645.775</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>https://judiciary.go.ug/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>circa 30 (Centri PJ)</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>114.333</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.poderjudicial.gub.uy/institucional/centros-de-mediacion.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>circa 1.900 (+3.000 formati)</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>18.379</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adliya.uz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>343 (mediatori commerciali)</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>284.169</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>https://tapchicongthuong.vn/phap-luat-ve-hoa-giai-thuong-mai-tu-thuc-tien-thanh-pho-ho-chi-minh-thuc-trang-va-giai-phap-103581.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
           <t>Zambia</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>190</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>102.474</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>registro professionale</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>https://judiciaryzambia.com/mediation-in-zambia-and-statistics/</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="72" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="76" ht="72" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>Conteggio «registro per registro» dei mediatori fuori dall'UE/UK, consultando ciascun registro ufficiale nazionale nella lingua ufficiale del luogo (ricerca luglio 2026). La densità è calcolata sulla popolazione nazionale. Le categorie «mediazione popolare/comunitaria» (Cina, Ruanda, Sri Lanka, Taiwan) e «dato sub-nazionale/parziale» (USA-Florida, Brasile) NON sono omogenee con i registri professionali e non vanno sommate. Per i Paesi non elencati non risulta pubblicato un conteggio ufficiale: N/D.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F50"/>
+  <autoFilter ref="A1:F75"/>
   <mergeCells count="1">
-    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A76:F76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/download/ricerca-mondiale-mediazione-tabelle.xlsx
+++ b/download/ricerca-mondiale-mediazione-tabelle.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Mediazioni per Paese'!$A$1:$D$196</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2-Mediatori e registri'!$A$1:$E$196</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4-Mediatori extra-UE'!$A$1:$F$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4-Mediatori extra-UE'!$A$1:$F$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>24 (Registre de Mediadors) (2023); 1 mediatore ogni 3.292 ab.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.govern.ad/ca/ministeris-i-secretaries-d-estat/ministeri-de-justicia-i-interior/area-d-entitats-juridiques-i-professions-titulades/llista-de-mediadors-inscrits-al-registre-de-mediadors</t>
         </is>
       </c>
     </row>
@@ -5246,12 +5246,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>40 (panel BIAC) (2025) [dato parziale/sub-nazionale]</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://biac.org.bd/list-of-mediators/</t>
         </is>
       </c>
     </row>
@@ -5273,12 +5273,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 13 (ADR Association) (2026); 1 mediatore ogni 21.615 ab.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://adrbarbados.org/our-mediators</t>
         </is>
       </c>
     </row>
@@ -6407,12 +6407,12 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>oltre 400 (PHILJA, dato datato) (2001); 1 mediatore ogni 277.625 ab.</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://philja.judiciary.gov.ph/</t>
         </is>
       </c>
     </row>
@@ -7568,12 +7568,12 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>5 (Amt für Justiz) (2025); 1 mediatore ogni 7.800 ab.</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.llv.li/serviceportal2/amtsstellen/amt-fuer-justiz/mediation/liste-der-eingetragenen-mediatoren.pdf</t>
         </is>
       </c>
     </row>
@@ -7649,12 +7649,12 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>45 (Camera dei mediatori) (2024); 1 mediatore ogni 46.000 ab.</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.kmrsm.org.mk/medijatori/</t>
         </is>
       </c>
     </row>
@@ -7838,12 +7838,12 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 50 attivi (oltre 200 formati) (2023); 1 mediatore ogni 741.600 ab.</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.cfcim.org/une-nouvelle-loi-encadrant-le-processus-de-mediation/</t>
         </is>
       </c>
     </row>
@@ -7865,12 +7865,12 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>16 (CIMAM) (2026); 1 mediatore ogni 288.750 ab.</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://cimam.net/index.php/fr/services-3/mediation/liste-des-mediateurs</t>
         </is>
       </c>
     </row>
@@ -8162,12 +8162,12 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>2.054 (Mediation Council) (2026); 1 mediatore ogni 14.620 ab.</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://mediationcouncil.gov.np/pages/view/melmilap_karta</t>
         </is>
       </c>
     </row>
@@ -8189,12 +8189,12 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 216 (52 centri DIRAC) (2018); 1 mediatore ogni 31.713 ab.</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.poderjudicial.gob.ni/dirac22/centros_Activos.pdf</t>
         </is>
       </c>
     </row>
@@ -8297,12 +8297,12 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>oltre 1.000 (membri AMINZ, incl. arbitri) (2025); 1 mediatore ogni 5.120 ab.</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.aminz.org.nz/about-us</t>
         </is>
       </c>
     </row>
@@ -8324,12 +8324,12 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>2 (OCAC) (2026); 1 mediatore ogni 2.260.000 ab.</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://omanarbitration.om/ar/</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 400 (formati, Poder Judicial) (2024); 1 mediatore ogni 27.800 ab.</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://poderjudicial.gob.do/</t>
         </is>
       </c>
     </row>
@@ -9454,12 +9454,12 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 8 (prima coorte civile) (2025); 1 mediatore ogni 76.250 ab.</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://dwtonline.com/eerste-lichting-gecertificeerde-mediators-klaar-voor-inzet-in-suriname/</t>
         </is>
       </c>
     </row>
@@ -9724,12 +9724,12 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>9 (roster DRC) (2024) [dato parziale/sub-nazionale]</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://disputeresolutioncentre.org.tt/mediators-2/</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -11521,22 +11521,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Arabia Saudita</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>circa 17.000 (iscritti MoJ)</t>
+          <t>24 (Registre de Mediadors)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2.079</t>
+          <t>3.292</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -11546,29 +11546,29 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://www.moj.gov.sa/</t>
+          <t>https://www.govern.ad/ca/ministeris-i-secretaries-d-estat/ministeri-de-justicia-i-interior/area-d-entitats-juridiques-i-professions-titulades/llista-de-mediadors-inscrits-al-registre-de-mediadors</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Arabia Saudita</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>4.513 (dato ufficiale 2008)</t>
+          <t>circa 17.000 (iscritti MoJ)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10.151</t>
+          <t>2.079</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -11578,29 +11578,29 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/55000-59999/59525/norma.htm</t>
+          <t>https://www.moj.gov.sa/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>4.513 (dato ufficiale 2008)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22.683</t>
+          <t>10.151</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -11610,19 +11610,19 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://www.moj.am/page/582</t>
+          <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/55000-59999/59525/norma.htm</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>circa 4.000</t>
+          <t>123</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6.422</t>
+          <t>22.683</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -11642,19 +11642,19 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://msb.org.au/resources/faqs</t>
+          <t>https://www.moj.am/page/582</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Azerbaigian</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>circa 4.000</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26.614</t>
+          <t>6.422</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -11674,19 +11674,19 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://mediasiya.gov.az/</t>
+          <t>https://msb.org.au/resources/faqs</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Azerbaigian</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21 (BCC)</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>83.333</t>
+          <t>26.614</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -11706,29 +11706,29 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://www.alayam.com/alayam/economic/1035195/News.html</t>
+          <t>https://mediasiya.gov.az/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Belize</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21 (BCC)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21.053</t>
+          <t>83.333</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -11738,19 +11738,19 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>https://www.belizejudiciary.org/court-connected-mediators/</t>
+          <t>https://www.alayam.com/alayam/economic/1035195/News.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>107 (lista CAMeC 2025-2027)</t>
+          <t>40 (panel BIAC)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -11760,71 +11760,71 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>116.355</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://camec.bj/</t>
+          <t>https://biac.org.bd/list-of-mediators/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>circa 2.870 (formati BNLI, cumulativo)</t>
+          <t>circa 13 (ADR Association)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>21.615</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>https://bnli.bt/wp-content/uploads/2023/02/CAM-2022.pdf</t>
+          <t>https://adrbarbados.org/our-mediators</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Bielorussia</t>
+          <t>Belize</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>circa 1.330</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7.023</t>
+          <t>21.053</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -11834,29 +11834,29 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://minjust.gov.by/directions/advocacy/mediation/list_register/</t>
+          <t>https://www.belizejudiciary.org/court-connected-mediators/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>circa 157 (conciliadores judiciales)</t>
+          <t>107 (lista CAMeC 2025-2027)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>75.350</t>
+          <t>116.355</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -11866,93 +11866,93 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>https://www.conciliacionbolivia.org/mapa-de-la-conciliacion</t>
+          <t>https://camec.bj/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Bosnia ed Erzegovina</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>oltre 160</t>
+          <t>circa 2.870 (formati BNLI, cumulativo)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>20.375</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://www.umbih.ba/index.php/medijacija/lista-medijatora</t>
+          <t>https://bnli.bt/wp-content/uploads/2023/02/CAM-2022.pdf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Brasile</t>
+          <t>Bielorussia</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>circa 1.747 (dato parziale 2017)</t>
+          <t>circa 1.330</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>122.496</t>
+          <t>7.023</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>dato sub-nazionale/parziale</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>https://conciliajud.cnj.jus.br/ccmj</t>
+          <t>https://minjust.gov.by/directions/advocacy/mediation/list_register/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Brunei</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>almeno 10 (BDAC)</t>
+          <t>circa 157 (conciliadores judiciales)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>44.000</t>
+          <t>75.350</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -11962,29 +11962,29 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://thebruneian.news/2025/02/23/bdac-brunei-darussalams-centre-for-alternative-dispute-resolution/</t>
+          <t>https://www.conciliacionbolivia.org/mapa-de-la-conciliacion</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Cambogia</t>
+          <t>Bosnia ed Erzegovina</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>16 (commerciali)</t>
+          <t>oltre 160</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1.045.000</t>
+          <t>20.375</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -11994,61 +11994,61 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>https://ncac.org.kh/en/services/mediation/list-of-mediators/</t>
+          <t>https://www.umbih.ba/index.php/medijacija/lista-medijatora</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Camerun</t>
+          <t>Brasile</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>circa 20 (CMAG/OHADA)</t>
+          <t>circa 1.747 (dato parziale 2017)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1.360.000</t>
+          <t>122.496</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://www.ohada.com/actualite/5238/</t>
+          <t>https://conciliajud.cnj.jus.br/ccmj</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Brunei</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>oltre 2.400 (mediatori+arbitri)</t>
+          <t>almeno 10 (BDAC)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15.938</t>
+          <t>44.000</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -12058,61 +12058,61 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>https://mediators.ca/our-adr-partners</t>
+          <t>https://thebruneian.news/2025/02/23/bdac-brunei-darussalams-centre-for-alternative-dispute-resolution/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Cina</t>
+          <t>Cambogia</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>3.176.000 mediatori popolari</t>
+          <t>16 (commerciali)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>1.045.000</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://www.moj.gov.cn/</t>
+          <t>https://ncac.org.kh/en/services/mediation/list-of-mediators/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Camerun</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>3.680–6.743</t>
+          <t>circa 20 (CMAG/OHADA)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2020-2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>10.254</t>
+          <t>1.360.000</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -12122,93 +12122,93 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://www.sicaac.gov.co/</t>
+          <t>https://www.ohada.com/actualite/5238/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Corea del Sud</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>circa 5.000 (conciliatori giudiziari)</t>
+          <t>oltre 2.400 (mediatori+arbitri)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10.348</t>
+          <t>15.938</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>http://www.cbinews.co.kr/news/articleView.html?idxno=20699</t>
+          <t>https://mediators.ca/our-adr-partners</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Costa d'Avorio</t>
+          <t>Cina</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>16-21 (CACI)</t>
+          <t>3.176.000 mediatori popolari</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1.690.625</t>
+          <t>445</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://news.abidjan.net/articles/726030</t>
+          <t>https://www.moj.gov.cn/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3.680–6.743</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2020-2023</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1.119.000</t>
+          <t>10.254</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -12218,93 +12218,93 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>http://www.cubadebate.cu/noticias/2025/01/16/toman-posesion-arbitros-y-mediadores-de-la-corte-cubana-de-arbitraje-comercial-internacional/</t>
+          <t>https://www.sicaac.gov.co/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Dominica</t>
+          <t>Congo</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>52 (arbitri+mediatori, dato combinato)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5.143</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>https://www.eccourts.org/court-connected-mediation</t>
+          <t>http://unicongo.cg/2021/11/J-ECO-10</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Corea del Sud</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>circa 5.000 (conciliatori giudiziari)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>5.050</t>
+          <t>10.348</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://www.funcionjudicial.gob.ec/</t>
+          <t>http://www.cbinews.co.kr/news/articleView.html?idxno=20699</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Egitto</t>
+          <t>Costa d'Avorio</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>circa 80 (panel CRCICA)</t>
+          <t>16-21 (CACI)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1.303.750</t>
+          <t>1.690.625</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -12314,29 +12314,29 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>https://crcica.org/mediation/panel-of-mediators/</t>
+          <t>https://news.abidjan.net/articles/726030</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>El Salvador</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>30.905</t>
+          <t>1.119.000</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -12346,14 +12346,14 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://www.pgr.gob.sv/procuraduria-especializada-de-mediacion-y-conciliacion/</t>
+          <t>http://www.cubadebate.cu/noticias/2025/01/16/toman-posesion-arbitros-y-mediadores-de-la-corte-cubana-de-arbitraje-comercial-internacional/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Figi</t>
+          <t>Dominica</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -12363,12 +12363,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>64.286</t>
+          <t>5.143</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -12378,29 +12378,29 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://fijimediation.org/</t>
+          <t>https://www.eccourts.org/court-connected-mediation</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>circa 30 (IIMAC)</t>
+          <t>3.525</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>76.667</t>
+          <t>5.050</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -12410,29 +12410,29 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://gabonactu.com/blog/2023/12/25/dix-mediateurs-daffaires-recoivent-des-certificats-de-liimac/</t>
+          <t>https://www.funcionjudicial.gob.ec/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Egitto</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>circa 18 (Judiciary CC-ADR)</t>
+          <t>circa 80 (panel CRCICA)</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>138.333</t>
+          <t>1.303.750</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -12442,19 +12442,19 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>https://judiciary.gov.gm/court-connected</t>
+          <t>https://crcica.org/mediation/panel-of-mediators/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>El Salvador</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>circa 170</t>
+          <t>210</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>21.824</t>
+          <t>30.905</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -12474,61 +12474,61 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://mediators.ge/</t>
+          <t>https://www.pgr.gob.sv/procuraduria-especializada-de-mediacion-y-conciliacion/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Emirati Arabi Uniti</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>58+ (solo Abu Dhabi ADJD)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>48.929</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>https://mofep.gov.gh/</t>
+          <t>https://www.adjd.gov.ae/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Giamaica</t>
+          <t>Figi</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>37.237</t>
+          <t>64.286</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -12538,29 +12538,29 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://www.disputeresolutionfoundation.org/</t>
+          <t>https://fijimediation.org/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Filippine</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>circa 100 (Unidad RAC OJ)</t>
+          <t>oltre 400 (PHILJA, dato datato)</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>176.000</t>
+          <t>277.625</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -12570,29 +12570,29 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>http://asies.org.gt/pdf/201310_diagnostico_centros_de_mediacion_rac_daj.pdf</t>
+          <t>https://philja.judiciary.gov.ph/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>circa 1.900 (HKMAAL)</t>
+          <t>circa 30 (IIMAC)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3.937</t>
+          <t>76.667</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -12602,29 +12602,29 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://www.hkmaal.org.hk/</t>
+          <t>https://gabonactu.com/blog/2023/12/25/dix-mediateurs-daffaires-recoivent-des-certificats-de-liimac/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>16.565 (formati)</t>
+          <t>circa 18 (Judiciary CC-ADR)</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2021-2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>84.093</t>
+          <t>138.333</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -12634,61 +12634,61 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>https://mcpc.nic.in/</t>
+          <t>https://judiciary.gov.gm/court-connected</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>circa 16.000 (Consigli risoluzione controversie)</t>
+          <t>circa 170</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>5.495</t>
+          <t>21.824</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://mehrnews.com/news/6308238/</t>
+          <t>https://mediators.ge/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Israele</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>circa 300 (lista giudiziaria)</t>
+          <t>635</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>31.500</t>
+          <t>48.929</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -12698,29 +12698,29 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>https://www.gov.il/he/pages/mediation_department</t>
+          <t>https://mofep.gov.gh/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Kazakistan</t>
+          <t>Giamaica</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>371 professionali (+4.465 comunitari)</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>51.213</t>
+          <t>37.237</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -12730,29 +12730,29 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://mediator.kz/reestr</t>
+          <t>https://www.disputeresolutionfoundation.org/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>circa 900 attivi</t>
+          <t>circa 100 (Unidad RAC OJ)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2023-2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>58.900</t>
+          <t>176.000</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -12762,29 +12762,29 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>https://judiciary.go.ke/list-of-accredited-mediators/</t>
+          <t>http://asies.org.gt/pdf/201310_diagnostico_centros_de_mediacion_rac_daj.pdf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Kirghizistan</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>circa 1.900 (HKMAAL)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>24.686</t>
+          <t>3.937</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -12794,29 +12794,29 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://mediator.kg/mediators/</t>
+          <t>https://www.hkmaal.org.hk/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Kosovo</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>16.565 (formati)</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021-2022</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>9.471</t>
+          <t>84.093</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -12826,93 +12826,93 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>https://ndermjetesimi.com/en/historiku/</t>
+          <t>https://mcpc.nic.in/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Macedonia del Nord</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>circa 45 (Camera KMRSM)</t>
+          <t>oltre 2.000 (dato parziale)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>46.000</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>https://www.kmrsm.org.mk/medijatori/</t>
+          <t>https://www.hukumonline.com/berita/a/lt62ff0e1b4d1d1/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Malesia</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>113 (panel MIMC)</t>
+          <t>circa 16.000 (Consigli risoluzione controversie)</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>297.080</t>
+          <t>5.495</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>https://www.mimc.org.my/list-of-accredited-mediators/</t>
+          <t>https://mehrnews.com/news/6308238/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Israele</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>circa 300 (lista giudiziaria)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2.682</t>
+          <t>31.500</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -12922,19 +12922,19 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://mediere.gov.md/sites/default/files/document/attachments/registrul_atestatelor_mediatorilor_2.pdf</t>
+          <t>https://www.gov.il/he/pages/mediation_department</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Kazakistan</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>circa 400</t>
+          <t>371 professionali (+4.465 comunitari)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>8.375</t>
+          <t>51.213</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -12954,29 +12954,29 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>https://www.judcouncil.mn/</t>
+          <t>https://mediator.kz/reestr</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>circa 900 attivi</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2023-2025</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>2.650</t>
+          <t>58.900</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -12986,29 +12986,29 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>https://www.cazrs.me/</t>
+          <t>https://judiciary.go.ke/list-of-accredited-mediators/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Norvegia</t>
+          <t>Kirghizistan</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>circa 65 (mediazione familiare)</t>
+          <t>271</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>83.231</t>
+          <t>24.686</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -13018,29 +13018,29 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>https://www.bufdir.no/</t>
+          <t>https://mediator.kg/mediators/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Kosovo</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>113.559</t>
+          <t>9.471</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -13050,29 +13050,29 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>https://www.pj.gov.py/contenido/150-direccion-de-mediacion/1198</t>
+          <t>https://ndermjetesimi.com/en/historiku/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Perù</t>
+          <t>Liechtenstein</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>circa 58.738 conciliatori extragiudiziali</t>
+          <t>5 (Amt für Justiz)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>7.800</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -13082,29 +13082,29 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>https://laley.pe/art/6527/existen-mas-de-52-mil-conciliadores-extrajudiciales-a-nivel-nacional</t>
+          <t>https://www.llv.li/serviceportal2/amtsstellen/amt-fuer-justiz/mediation/liste-der-eingetragenen-mediatoren.pdf</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Macedonia</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>6 (panel QICDRC)</t>
+          <t>45 (Camera dei mediatori)</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>448.333</t>
+          <t>46.000</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -13114,61 +13114,61 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>https://www.qicdrc.gov.qa/services/mediation</t>
+          <t>https://www.kmrsm.org.mk/medijatori/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Ruanda</t>
+          <t>Macedonia del Nord</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>circa 30.000 Abunzi</t>
+          <t>circa 45 (Camera KMRSM)</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>46.000</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>https://weinsteininternational.org/</t>
+          <t>https://www.kmrsm.org.mk/medijatori/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Samoa</t>
+          <t>Malesia</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>circa 47 (AMSA)</t>
+          <t>113 (panel MIMC)</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>4.681</t>
+          <t>297.080</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -13178,29 +13178,29 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>https://www.samoaobserver.ws/en/21_12_2017/local/28089/Twenty-four-Mediators-graduate.htm</t>
+          <t>https://www.mimc.org.my/list-of-accredited-mediators/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Santa Lucia</t>
+          <t>Marocco</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>circa 41</t>
+          <t>circa 50 attivi (oltre 200 formati)</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>4.390</t>
+          <t>741.600</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -13210,19 +13210,19 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/item/global-legal-monitor/2017-06-12/saint-lucia-awareness-campaign-on-mediation-launched/</t>
+          <t>https://www.cfcim.org/une-nouvelle-loi-encadrant-le-processus-de-mediation/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Mauritania</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>29 (CAMC Dakar)</t>
+          <t>16 (CIMAM)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>582.069</t>
+          <t>288.750</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -13242,61 +13242,61 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>https://arbitrage-senegal.com/liste-des-mediateurs/</t>
+          <t>https://cimam.net/index.php/fr/services-3/mediation/liste-des-mediateurs</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Messico</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>oltre 1.100</t>
+          <t>649 (solo Città del Messico)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>6.209</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>https://mpravde.gov.rs/registar-posrednika</t>
+          <t>https://www.poderjudicialcdmx.gob.mx/cja/mediacion-privada-2/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>oltre 500 (SIMI)</t>
+          <t>977</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>10.900</t>
+          <t>2.682</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -13306,93 +13306,93 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>https://www.simi.org.sg/</t>
+          <t>https://mediere.gov.md/sites/default/files/document/attachments/registrul_atestatelor_mediatorilor_2.pdf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>oltre 8.600</t>
+          <t>circa 400</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>2.577</t>
+          <t>8.375</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>https://mediation.gov.lk/en/</t>
+          <t>https://www.judcouncil.mn/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Stati Uniti (Florida)</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>5.674 (solo Florida)</t>
+          <t>234</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>3.839</t>
+          <t>2.650</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>dato sub-nazionale/parziale</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>https://www.flcourts.gov/Resources-Services/Alternative-Dispute-Resolution/</t>
+          <t>https://www.cazrs.me/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Sudafrica</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>233 (court-annexed, DOJ)</t>
+          <t>2.054 (Mediation Council)</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>254.893</t>
+          <t>14.620</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -13402,29 +13402,29 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>https://www.justice.gov.za/mediation/mediation.html</t>
+          <t>https://mediationcouncil.gov.np/pages/view/melmilap_karta</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Svizzera</t>
+          <t>Nicaragua</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>oltre 1.500 (FSM); ~200 SKWM</t>
+          <t>circa 216 (52 centri DIRAC)</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>5.800</t>
+          <t>31.713</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -13434,61 +13434,61 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>https://www.mediation-ch.org/</t>
+          <t>https://www.poderjudicial.gob.ni/dirac22/centros_Activos.pdf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Norvegia</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>circa 4.054 (conciliatori township)</t>
+          <t>circa 65 (mediazione familiare)</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>5.814</t>
+          <t>83.231</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.tw/dataset/13947</t>
+          <t>https://www.bufdir.no/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Nuova Zelanda</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>7 (Comitato CATO)</t>
+          <t>oltre 1.000 (membri AMINZ, incl. arbitri)</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1.211.429</t>
+          <t>5.120</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -13498,29 +13498,29 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>https://cato.tg/</t>
+          <t>https://www.aminz.org.nz/about-us</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>11 (mediatori bancari)</t>
+          <t>2 (OCAC)</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>1.114.545</t>
+          <t>2.260.000</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -13530,61 +13530,61 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>https://www.cbf.org.tn/contacts-des-mediateurs-2/</t>
+          <t>https://omanarbitration.om/ar/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Turchia</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>circa 45.154</t>
+          <t>circa 114 (solo centro MICADR)</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1.878</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>https://adb.adalet.gov.tr/</t>
+          <t>https://www.micadr.com/accredited-mediator-2/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Tuvalu</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>3 (Office People's Lawyer)</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>3.667</t>
+          <t>113.559</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -13594,29 +13594,29 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>https://disputescentre.com.au/mediation-in-the-south-pacific-islands/</t>
+          <t>https://www.pj.gov.py/contenido/150-direccion-de-mediacion/1198</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Ucraina</t>
+          <t>Perù</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>circa 160 (NAMU)</t>
+          <t>circa 58.738 conciliatori extragiudiziali</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>273.688</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -13626,29 +13626,29 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>http://namu.com.ua/ua/members/</t>
+          <t>https://laley.pe/art/6527/existen-mas-de-52-mil-conciliadores-extrajudiciales-a-nivel-nacional</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>6 (panel QICDRC)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>645.775</t>
+          <t>448.333</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -13658,29 +13658,29 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>https://judiciary.go.ug/</t>
+          <t>https://www.qicdrc.gov.qa/services/mediation</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Repubblica Dominicana</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>circa 30 (Centri PJ)</t>
+          <t>circa 400 (formati, Poder Judicial)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>114.333</t>
+          <t>27.800</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -13690,117 +13690,789 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>https://www.poderjudicial.gub.uy/institucional/centros-de-mediacion.html</t>
+          <t>https://poderjudicial.gob.do/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Ruanda</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>circa 1.900 (+3.000 formati)</t>
+          <t>circa 30.000 Abunzi</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>18.379</t>
+          <t>449</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>https://www.adliya.uz/</t>
+          <t>https://weinsteininternational.org/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>343 (mediatori commerciali)</t>
+          <t>oltre 100 (unica SRO registrata)</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>284.169</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>https://tapchicongthuong.vn/phap-luat-ve-hoa-giai-thuong-mai-tu-thuc-tien-thanh-pho-ho-chi-minh-thuc-trang-va-giai-phap-103581.htm</t>
+          <t>https://www.all-sro.ru/register/sromed/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>Samoa</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>circa 47 (AMSA)</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>4.681</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.samoaobserver.ws/en/21_12_2017/local/28089/Twenty-four-Mediators-graduate.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Santa Lucia</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>circa 41</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>4.390</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.loc.gov/item/global-legal-monitor/2017-06-12/saint-lucia-awareness-campaign-on-mediation-launched/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>29 (CAMC Dakar)</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>582.069</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>https://arbitrage-senegal.com/liste-des-mediateurs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>oltre 1.100</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>6.209</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>https://mpravde.gov.rs/registar-posrednika</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>oltre 500 (SIMI)</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>10.900</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.simi.org.sg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>oltre 8.600</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>2.577</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>mediazione popolare/comunitaria</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>https://mediation.gov.lk/en/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Stati Uniti (Florida)</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>5.674 (solo Florida)</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>3.839</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>dato sub-nazionale/parziale</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flcourts.gov/Resources-Services/Alternative-Dispute-Resolution/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Sudafrica</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>233 (court-annexed, DOJ)</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>254.893</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.za/mediation/mediation.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Suriname</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>circa 8 (prima coorte civile)</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>76.250</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>https://dwtonline.com/eerste-lichting-gecertificeerde-mediators-klaar-voor-inzet-in-suriname/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Svizzera</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>oltre 1.500 (FSM); ~200 SKWM</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>5.800</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mediation-ch.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>circa 4.054 (conciliatori township)</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>5.814</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>mediazione popolare/comunitaria</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>https://data.gov.tw/dataset/13947</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Togo</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>7 (Comitato CATO)</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>1.211.429</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>https://cato.tg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Trinidad e Tobago</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>9 (roster DRC)</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>dato sub-nazionale/parziale</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>https://disputeresolutioncentre.org.tt/mediators-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>11 (mediatori bancari)</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>1.114.545</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cbf.org.tn/contacts-des-mediateurs-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Turchia</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>circa 45.154</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>1.878</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>https://adb.adalet.gov.tr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Tuvalu</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>3 (Office People's Lawyer)</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>3.667</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>https://disputescentre.com.au/mediation-in-the-south-pacific-islands/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Ucraina</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>circa 160 (NAMU)</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>273.688</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>http://namu.com.ua/ua/members/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>645.775</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>https://judiciary.go.ug/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>circa 30 (Centri PJ)</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>114.333</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.poderjudicial.gub.uy/institucional/centros-de-mediacion.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>circa 1.900 (+3.000 formati)</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18.379</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adliya.uz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>343 (mediatori commerciali)</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>284.169</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>https://tapchicongthuong.vn/phap-luat-ve-hoa-giai-thuong-mai-tu-thuc-tien-thanh-pho-ho-chi-minh-thuc-trang-va-giai-phap-103581.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
           <t>Zambia</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>190</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>102.474</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>registro professionale</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>https://judiciaryzambia.com/mediation-in-zambia-and-statistics/</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="72" customHeight="1">
-      <c r="A76" s="4" t="inlineStr">
+    <row r="97" ht="72" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>Conteggio «registro per registro» dei mediatori fuori dall'UE/UK, consultando ciascun registro ufficiale nazionale nella lingua ufficiale del luogo (ricerca luglio 2026). La densità è calcolata sulla popolazione nazionale. Le categorie «mediazione popolare/comunitaria» (Cina, Ruanda, Sri Lanka, Taiwan) e «dato sub-nazionale/parziale» (USA-Florida, Brasile) NON sono omogenee con i registri professionali e non vanno sommate. Per i Paesi non elencati non risulta pubblicato un conteggio ufficiale: N/D.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F75"/>
+  <autoFilter ref="A1:F96"/>
   <mergeCells count="1">
-    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A97:F97"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/download/ricerca-mondiale-mediazione-tabelle.xlsx
+++ b/download/ricerca-mondiale-mediazione-tabelle.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Mediazioni per Paese'!$A$1:$D$196</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2-Mediatori e registri'!$A$1:$E$196</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4-Mediatori extra-UE'!$A$1:$F$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4-Mediatori extra-UE'!$A$1:$F$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5030,12 +5030,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>circa 17.000 (iscritti MoJ) (2020); 1 mediatore ogni 2.079 ab.</t>
+          <t>720 conciliatori certificati (piattaforma Taradhi) (2024); 1 mediatore ogni 49.083 ab.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.moj.gov.sa/</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.alwatan.com.sa/article/1149714</t>
         </is>
       </c>
     </row>
@@ -5678,12 +5678,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>circa 20 (CMAG/OHADA) (2019); 1 mediatore ogni 1.360.000 ab.</t>
+          <t>12 (lista CMAG dic. 2024) (2024); 1 mediatore ogni 2.266.667 ab.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.ohada.com/actualite/5238/</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://legecam.cm/wp-content/uploads/2024/12/Liste-des-mediateurs-references-au-CMAG.pdf</t>
         </is>
       </c>
     </row>
@@ -6380,12 +6380,12 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>14 (2016); 1 mediatore ogni 64.286 ab.</t>
+          <t>circa 50 (Fiji Mediation Centre) (2023); 1 mediatore ogni 18.000 ab.</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://fijimediation.org/</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://fijimediation.org/team-of-experts/</t>
         </is>
       </c>
     </row>
@@ -6596,12 +6596,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>635 (2021); 1 mediatore ogni 48.929 ab.</t>
+          <t>336 (rete Court-Connected ADR) (2026); 1 mediatore ogni 92.470 ab.</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://mofep.gov.gh/</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://gna.org.gh/2026/03/chief-justice-launches-adr-week-in-sunyani/</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>19.212 (comitati di conciliazione, chotei-in) (2025); 1 mediatore ogni 6.543 ab. [mediazione popolare/comunitaria]</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.choutei.jp/about/chouteiin/index.html</t>
         </is>
       </c>
     </row>
@@ -7001,12 +7001,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>16.565 (formati) (2021-2022); 1 mediatore ogni 84.093 ab.</t>
+          <t>circa 20.000 (formati, MCPC/NALSA) (2025); 1 mediatore ogni 69.650 ab.</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://mcpc.nic.in/</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.livelaw.in/articles/mediation-for-the-nation-lessons-learnt-535455</t>
         </is>
       </c>
     </row>
@@ -7136,12 +7136,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>58 (Sátt) (2026); 1 mediatore ogni 6.414 ab.</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.satt.is/team</t>
         </is>
       </c>
     </row>
@@ -8054,12 +8054,12 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>52 (CACM) (2026); 1 mediatore ogni 616.923 ab.</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.cacm.org.mz/?page_id=4379</t>
         </is>
       </c>
     </row>
@@ -8270,12 +8270,12 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>circa 65 (mediazione familiare) (2016); 1 mediatore ogni 83.231 ab.</t>
+          <t>circa 550 (konfliktråd) + ~65 familiari (2024); 1 mediatore ogni 9.836 ab.</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.bufdir.no/</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://konfliktraadet.no/en/about-us/</t>
         </is>
       </c>
     </row>
@@ -8459,12 +8459,12 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>circa 1.414 generali (+625 comunitari) (2019); 1 mediatore ogni 3.098 ab.</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.datosabiertos.gob.pa/dataset/mingob-drac-registro-de-mediadores-y-conciliadores-del-mes-febrero-2019</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -11558,17 +11558,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>circa 17.000 (iscritti MoJ)</t>
+          <t>720 conciliatori certificati (piattaforma Taradhi)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2.079</t>
+          <t>49.083</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -11578,7 +11578,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://www.moj.gov.sa/</t>
+          <t>https://www.alwatan.com.sa/article/1149714</t>
         </is>
       </c>
     </row>
@@ -12102,17 +12102,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>circa 20 (CMAG/OHADA)</t>
+          <t>12 (lista CMAG dic. 2024)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1.360.000</t>
+          <t>2.266.667</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -12122,7 +12122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://www.ohada.com/actualite/5238/</t>
+          <t>https://legecam.cm/wp-content/uploads/2024/12/Liste-des-mediateurs-references-au-CMAG.pdf</t>
         </is>
       </c>
     </row>
@@ -12518,17 +12518,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>circa 50 (Fiji Mediation Centre)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>64.286</t>
+          <t>18.000</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -12538,7 +12538,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://fijimediation.org/</t>
+          <t>https://fijimediation.org/team-of-experts/</t>
         </is>
       </c>
     </row>
@@ -12678,17 +12678,17 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>336 (rete Court-Connected ADR)</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>48.929</t>
+          <t>92.470</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>https://mofep.gov.gh/</t>
+          <t>https://gna.org.gh/2026/03/chief-justice-launches-adr-week-in-sunyani/</t>
         </is>
       </c>
     </row>
@@ -12737,54 +12737,54 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Giappone</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>circa 100 (Unidad RAC OJ)</t>
+          <t>19.212 (comitati di conciliazione, chotei-in)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>176.000</t>
+          <t>6.543</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>http://asies.org.gt/pdf/201310_diagnostico_centros_de_mediacion_rac_daj.pdf</t>
+          <t>https://www.choutei.jp/about/chouteiin/index.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>circa 1.900 (HKMAAL)</t>
+          <t>circa 100 (Unidad RAC OJ)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>3.937</t>
+          <t>176.000</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -12794,29 +12794,29 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://www.hkmaal.org.hk/</t>
+          <t>http://asies.org.gt/pdf/201310_diagnostico_centros_de_mediacion_rac_daj.pdf</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16.565 (formati)</t>
+          <t>circa 1.900 (HKMAAL)</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2021-2022</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>84.093</t>
+          <t>3.937</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -12826,83 +12826,83 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>https://mcpc.nic.in/</t>
+          <t>https://www.hkmaal.org.hk/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>oltre 2.000 (dato parziale)</t>
+          <t>circa 20.000 (formati, MCPC/NALSA)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>69.650</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>dato sub-nazionale/parziale</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>https://www.hukumonline.com/berita/a/lt62ff0e1b4d1d1/</t>
+          <t>https://www.livelaw.in/articles/mediation-for-the-nation-lessons-learnt-535455</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>circa 16.000 (Consigli risoluzione controversie)</t>
+          <t>oltre 2.000 (dato parziale)</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>5.495</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>https://mehrnews.com/news/6308238/</t>
+          <t>https://www.hukumonline.com/berita/a/lt62ff0e1b4d1d1/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Israele</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>circa 300 (lista giudiziaria)</t>
+          <t>circa 16.000 (Consigli risoluzione controversie)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -12912,39 +12912,39 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>31.500</t>
+          <t>5.495</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://www.gov.il/he/pages/mediation_department</t>
+          <t>https://mehrnews.com/news/6308238/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Kazakistan</t>
+          <t>Islanda</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>371 professionali (+4.465 comunitari)</t>
+          <t>58 (Sátt)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>51.213</t>
+          <t>6.414</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -12954,29 +12954,29 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>https://mediator.kz/reestr</t>
+          <t>https://www.satt.is/team</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Israele</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>circa 900 attivi</t>
+          <t>circa 300 (lista giudiziaria)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2023-2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>58.900</t>
+          <t>31.500</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -12986,29 +12986,29 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>https://judiciary.go.ke/list-of-accredited-mediators/</t>
+          <t>https://www.gov.il/he/pages/mediation_department</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Kirghizistan</t>
+          <t>Kazakistan</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>371 professionali (+4.465 comunitari)</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>24.686</t>
+          <t>51.213</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -13018,29 +13018,29 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>https://mediator.kg/mediators/</t>
+          <t>https://mediator.kz/reestr</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Kosovo</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>circa 900 attivi</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2023-2025</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>9.471</t>
+          <t>58.900</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -13050,29 +13050,29 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>https://ndermjetesimi.com/en/historiku/</t>
+          <t>https://judiciary.go.ke/list-of-accredited-mediators/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Liechtenstein</t>
+          <t>Kirghizistan</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>5 (Amt für Justiz)</t>
+          <t>271</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>7.800</t>
+          <t>24.686</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -13082,29 +13082,29 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>https://www.llv.li/serviceportal2/amtsstellen/amt-fuer-justiz/mediation/liste-der-eingetragenen-mediatoren.pdf</t>
+          <t>https://mediator.kg/mediators/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Macedonia</t>
+          <t>Kosovo</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>45 (Camera dei mediatori)</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>46.000</t>
+          <t>9.471</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -13114,29 +13114,29 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>https://www.kmrsm.org.mk/medijatori/</t>
+          <t>https://ndermjetesimi.com/en/historiku/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Macedonia del Nord</t>
+          <t>Liechtenstein</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>circa 45 (Camera KMRSM)</t>
+          <t>5 (Amt für Justiz)</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>46.000</t>
+          <t>7.800</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -13146,29 +13146,29 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>https://www.kmrsm.org.mk/medijatori/</t>
+          <t>https://www.llv.li/serviceportal2/amtsstellen/amt-fuer-justiz/mediation/liste-der-eingetragenen-mediatoren.pdf</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Malesia</t>
+          <t>Macedonia</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>113 (panel MIMC)</t>
+          <t>45 (Camera dei mediatori)</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>297.080</t>
+          <t>46.000</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -13178,29 +13178,29 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>https://www.mimc.org.my/list-of-accredited-mediators/</t>
+          <t>https://www.kmrsm.org.mk/medijatori/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Marocco</t>
+          <t>Macedonia del Nord</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>circa 50 attivi (oltre 200 formati)</t>
+          <t>circa 45 (Camera KMRSM)</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>741.600</t>
+          <t>46.000</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -13210,19 +13210,19 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfcim.org/une-nouvelle-loi-encadrant-le-processus-de-mediation/</t>
+          <t>https://www.kmrsm.org.mk/medijatori/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Mauritania</t>
+          <t>Malesia</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16 (CIMAM)</t>
+          <t>113 (panel MIMC)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>288.750</t>
+          <t>297.080</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -13242,61 +13242,61 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>https://cimam.net/index.php/fr/services-3/mediation/liste-des-mediateurs</t>
+          <t>https://www.mimc.org.my/list-of-accredited-mediators/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Messico</t>
+          <t>Marocco</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>649 (solo Città del Messico)</t>
+          <t>circa 50 attivi (oltre 200 formati)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>741.600</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>dato sub-nazionale/parziale</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>https://www.poderjudicialcdmx.gob.mx/cja/mediacion-privada-2/</t>
+          <t>https://www.cfcim.org/une-nouvelle-loi-encadrant-le-processus-de-mediation/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Mauritania</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>16 (CIMAM)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2.682</t>
+          <t>288.750</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -13306,61 +13306,61 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>https://mediere.gov.md/sites/default/files/document/attachments/registrul_atestatelor_mediatorilor_2.pdf</t>
+          <t>https://cimam.net/index.php/fr/services-3/mediation/liste-des-mediateurs</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Messico</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>circa 400</t>
+          <t>649 (solo Città del Messico)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>8.375</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>https://www.judcouncil.mn/</t>
+          <t>https://www.poderjudicialcdmx.gob.mx/cja/mediacion-privada-2/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>977</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>2.650</t>
+          <t>2.682</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -13370,29 +13370,29 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>https://www.cazrs.me/</t>
+          <t>https://mediere.gov.md/sites/default/files/document/attachments/registrul_atestatelor_mediatorilor_2.pdf</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>2.054 (Mediation Council)</t>
+          <t>circa 400</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>14.620</t>
+          <t>8.375</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -13402,29 +13402,29 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>https://mediationcouncil.gov.np/pages/view/melmilap_karta</t>
+          <t>https://www.judcouncil.mn/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Nicaragua</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>circa 216 (52 centri DIRAC)</t>
+          <t>234</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>31.713</t>
+          <t>2.650</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -13434,29 +13434,29 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>https://www.poderjudicial.gob.ni/dirac22/centros_Activos.pdf</t>
+          <t>https://www.cazrs.me/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Norvegia</t>
+          <t>Mozambico</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>circa 65 (mediazione familiare)</t>
+          <t>52 (CACM)</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>83.231</t>
+          <t>616.923</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -13466,29 +13466,29 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>https://www.bufdir.no/</t>
+          <t>https://www.cacm.org.mz/?page_id=4379</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Nuova Zelanda</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>oltre 1.000 (membri AMINZ, incl. arbitri)</t>
+          <t>2.054 (Mediation Council)</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>5.120</t>
+          <t>14.620</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -13498,29 +13498,29 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>https://www.aminz.org.nz/about-us</t>
+          <t>https://mediationcouncil.gov.np/pages/view/melmilap_karta</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Nicaragua</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>2 (OCAC)</t>
+          <t>circa 216 (52 centri DIRAC)</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>2.260.000</t>
+          <t>31.713</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -13530,61 +13530,61 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>https://omanarbitration.om/ar/</t>
+          <t>https://www.poderjudicial.gob.ni/dirac22/centros_Activos.pdf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Norvegia</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>circa 114 (solo centro MICADR)</t>
+          <t>circa 550 (konfliktråd) + ~65 familiari</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>9.836</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>dato sub-nazionale/parziale</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>https://www.micadr.com/accredited-mediator-2/</t>
+          <t>https://konfliktraadet.no/en/about-us/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Nuova Zelanda</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>oltre 1.000 (membri AMINZ, incl. arbitri)</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>113.559</t>
+          <t>5.120</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -13594,29 +13594,29 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>https://www.pj.gov.py/contenido/150-direccion-de-mediacion/1198</t>
+          <t>https://www.aminz.org.nz/about-us</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Perù</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>circa 58.738 conciliatori extragiudiziali</t>
+          <t>2 (OCAC)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>2.260.000</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -13626,19 +13626,19 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>https://laley.pe/art/6527/existen-mas-de-52-mil-conciliadores-extrajudiciales-a-nivel-nacional</t>
+          <t>https://omanarbitration.om/ar/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>6 (panel QICDRC)</t>
+          <t>circa 114 (solo centro MICADR)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -13648,39 +13648,39 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>448.333</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>https://www.qicdrc.gov.qa/services/mediation</t>
+          <t>https://www.micadr.com/accredited-mediator-2/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Repubblica Dominicana</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>circa 400 (formati, Poder Judicial)</t>
+          <t>circa 1.414 generali (+625 comunitari)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>27.800</t>
+          <t>3.098</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -13690,93 +13690,93 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>https://poderjudicial.gob.do/</t>
+          <t>https://www.datosabiertos.gob.pa/dataset/mingob-drac-registro-de-mediadores-y-conciliadores-del-mes-febrero-2019</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Ruanda</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>circa 30.000 Abunzi</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>113.559</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>https://weinsteininternational.org/</t>
+          <t>https://www.pj.gov.py/contenido/150-direccion-de-mediacion/1198</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Perù</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>oltre 100 (unica SRO registrata)</t>
+          <t>circa 58.738 conciliatori extragiudiziali</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>dato sub-nazionale/parziale</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>https://www.all-sro.ru/register/sromed/</t>
+          <t>https://laley.pe/art/6527/existen-mas-de-52-mil-conciliadores-extrajudiciales-a-nivel-nacional</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Samoa</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>circa 47 (AMSA)</t>
+          <t>6 (panel QICDRC)</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>4.681</t>
+          <t>448.333</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -13786,29 +13786,29 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>https://www.samoaobserver.ws/en/21_12_2017/local/28089/Twenty-four-Mediators-graduate.htm</t>
+          <t>https://www.qicdrc.gov.qa/services/mediation</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Santa Lucia</t>
+          <t>Repubblica Dominicana</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>circa 41</t>
+          <t>circa 400 (formati, Poder Judicial)</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>4.390</t>
+          <t>27.800</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -13818,93 +13818,93 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/item/global-legal-monitor/2017-06-12/saint-lucia-awareness-campaign-on-mediation-launched/</t>
+          <t>https://poderjudicial.gob.do/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Ruanda</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>29 (CAMC Dakar)</t>
+          <t>circa 30.000 Abunzi</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>582.069</t>
+          <t>449</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>https://arbitrage-senegal.com/liste-des-mediateurs/</t>
+          <t>https://weinsteininternational.org/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>oltre 1.100</t>
+          <t>oltre 100 (unica SRO registrata)</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>6.209</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>https://mpravde.gov.rs/registar-posrednika</t>
+          <t>https://www.all-sro.ru/register/sromed/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Samoa</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>oltre 500 (SIMI)</t>
+          <t>circa 47 (AMSA)</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>10.900</t>
+          <t>4.681</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -13914,93 +13914,93 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>https://www.simi.org.sg/</t>
+          <t>https://www.samoaobserver.ws/en/21_12_2017/local/28089/Twenty-four-Mediators-graduate.htm</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Santa Lucia</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>oltre 8.600</t>
+          <t>circa 41</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>2.577</t>
+          <t>4.390</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>https://mediation.gov.lk/en/</t>
+          <t>https://www.loc.gov/item/global-legal-monitor/2017-06-12/saint-lucia-awareness-campaign-on-mediation-launched/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Stati Uniti (Florida)</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>5.674 (solo Florida)</t>
+          <t>29 (CAMC Dakar)</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>3.839</t>
+          <t>582.069</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>dato sub-nazionale/parziale</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>https://www.flcourts.gov/Resources-Services/Alternative-Dispute-Resolution/</t>
+          <t>https://arbitrage-senegal.com/liste-des-mediateurs/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Sudafrica</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>233 (court-annexed, DOJ)</t>
+          <t>oltre 1.100</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>254.893</t>
+          <t>6.209</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -14010,29 +14010,29 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>https://www.justice.gov.za/mediation/mediation.html</t>
+          <t>https://mpravde.gov.rs/registar-posrednika</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Suriname</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>circa 8 (prima coorte civile)</t>
+          <t>oltre 500 (SIMI)</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>76.250</t>
+          <t>10.900</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -14042,19 +14042,19 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>https://dwtonline.com/eerste-lichting-gecertificeerde-mediators-klaar-voor-inzet-in-suriname/</t>
+          <t>https://www.simi.org.sg/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Svizzera</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>oltre 1.500 (FSM); ~200 SKWM</t>
+          <t>oltre 8.600</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -14064,71 +14064,71 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>5.800</t>
+          <t>2.577</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>https://www.mediation-ch.org/</t>
+          <t>https://mediation.gov.lk/en/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Stati Uniti (Florida)</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>circa 4.054 (conciliatori township)</t>
+          <t>5.674 (solo Florida)</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>5.814</t>
+          <t>3.839</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.tw/dataset/13947</t>
+          <t>https://www.flcourts.gov/Resources-Services/Alternative-Dispute-Resolution/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Sudafrica</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>7 (Comitato CATO)</t>
+          <t>233 (court-annexed, DOJ)</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>1.211.429</t>
+          <t>254.893</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -14138,51 +14138,51 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>https://cato.tg/</t>
+          <t>https://www.justice.gov.za/mediation/mediation.html</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Trinidad e Tobago</t>
+          <t>Suriname</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>9 (roster DRC)</t>
+          <t>circa 8 (prima coorte civile)</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>76.250</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>dato sub-nazionale/parziale</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>https://disputeresolutioncentre.org.tt/mediators-2/</t>
+          <t>https://dwtonline.com/eerste-lichting-gecertificeerde-mediators-klaar-voor-inzet-in-suriname/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Svizzera</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>11 (mediatori bancari)</t>
+          <t>oltre 1.500 (FSM); ~200 SKWM</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -14192,7 +14192,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1.114.545</t>
+          <t>5.800</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -14202,61 +14202,61 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>https://www.cbf.org.tn/contacts-des-mediateurs-2/</t>
+          <t>https://www.mediation-ch.org/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Turchia</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>circa 45.154</t>
+          <t>circa 4.054 (conciliatori township)</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>1.878</t>
+          <t>5.814</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>https://adb.adalet.gov.tr/</t>
+          <t>https://data.gov.tw/dataset/13947</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Tuvalu</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>3 (Office People's Lawyer)</t>
+          <t>7 (Comitato CATO)</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>3.667</t>
+          <t>1.211.429</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -14266,19 +14266,19 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>https://disputescentre.com.au/mediation-in-the-south-pacific-islands/</t>
+          <t>https://cato.tg/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Ucraina</t>
+          <t>Trinidad e Tobago</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>circa 160 (NAMU)</t>
+          <t>9 (roster DRC)</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -14288,29 +14288,29 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>273.688</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>http://namu.com.ua/ua/members/</t>
+          <t>https://disputeresolutioncentre.org.tt/mediators-2/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>11 (mediatori bancari)</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>645.775</t>
+          <t>1.114.545</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -14330,29 +14330,29 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>https://judiciary.go.ug/</t>
+          <t>https://www.cbf.org.tn/contacts-des-mediateurs-2/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Turchia</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>circa 30 (Centri PJ)</t>
+          <t>circa 45.154</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>114.333</t>
+          <t>1.878</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -14362,29 +14362,29 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>https://www.poderjudicial.gub.uy/institucional/centros-de-mediacion.html</t>
+          <t>https://adb.adalet.gov.tr/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Tuvalu</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>circa 1.900 (+3.000 formati)</t>
+          <t>3 (Office People's Lawyer)</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>18.379</t>
+          <t>3.667</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -14394,29 +14394,29 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>https://www.adliya.uz/</t>
+          <t>https://disputescentre.com.au/mediation-in-the-south-pacific-islands/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Ucraina</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>343 (mediatori commerciali)</t>
+          <t>circa 160 (NAMU)</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>284.169</t>
+          <t>273.688</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -14426,53 +14426,181 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>https://tapchicongthuong.vn/phap-luat-ve-hoa-giai-thuong-mai-tu-thuc-tien-thanh-pho-ho-chi-minh-thuc-trang-va-giai-phap-103581.htm</t>
+          <t>http://namu.com.ua/ua/members/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>645.775</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>https://judiciary.go.ug/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>circa 30 (Centri PJ)</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>114.333</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.poderjudicial.gub.uy/institucional/centros-de-mediacion.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>circa 1.900 (+3.000 formati)</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>18.379</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adliya.uz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>343 (mediatori commerciali)</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>284.169</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>https://tapchicongthuong.vn/phap-luat-ve-hoa-giai-thuong-mai-tu-thuc-tien-thanh-pho-ho-chi-minh-thuc-trang-va-giai-phap-103581.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
           <t>Zambia</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>190</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>102.474</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>registro professionale</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>https://judiciaryzambia.com/mediation-in-zambia-and-statistics/</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="72" customHeight="1">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="101" ht="72" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>Conteggio «registro per registro» dei mediatori fuori dall'UE/UK, consultando ciascun registro ufficiale nazionale nella lingua ufficiale del luogo (ricerca luglio 2026). La densità è calcolata sulla popolazione nazionale. Le categorie «mediazione popolare/comunitaria» (Cina, Ruanda, Sri Lanka, Taiwan) e «dato sub-nazionale/parziale» (USA-Florida, Brasile) NON sono omogenee con i registri professionali e non vanno sommate. Per i Paesi non elencati non risulta pubblicato un conteggio ufficiale: N/D.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F96"/>
+  <autoFilter ref="A1:F100"/>
   <mergeCells count="1">
-    <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A101:F101"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/download/ricerca-mondiale-mediazione-tabelle.xlsx
+++ b/download/ricerca-mondiale-mediazione-tabelle.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Mediazioni per Paese'!$A$1:$D$196</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2-Mediatori e registri'!$A$1:$E$196</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4-Mediatori extra-UE'!$A$1:$F$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4-Mediatori extra-UE'!$A$1:$F$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>43.650 (bashingantahe, notabili-conciliatori di collina) (2021); 1 mediatore ogni 288 ab. [mediazione popolare/comunitaria]</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://burundi-eco.com/conseil-des-notables-collinaires-renforcement-ou-rehabilitation-de-linstitution-des-bashingantahe/</t>
         </is>
       </c>
     </row>
@@ -6947,12 +6947,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>oltre 400 (mediatori comunitari, 18 CRECs) (2022); 1 mediatore ogni 25.700 ab. [mediazione popolare/comunitaria]</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.undp.org/es/honduras/noticias/fortalecen-18-centros-de-resolucion-extrajudicial-de-conflictos-nivel-nacional</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -12065,54 +12065,54 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Cambogia</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>16 (commerciali)</t>
+          <t>43.650 (bashingantahe, notabili-conciliatori di collina)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1.045.000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://ncac.org.kh/en/services/mediation/list-of-mediators/</t>
+          <t>https://burundi-eco.com/conseil-des-notables-collinaires-renforcement-ou-rehabilitation-de-linstitution-des-bashingantahe/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Camerun</t>
+          <t>Cambogia</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>12 (lista CMAG dic. 2024)</t>
+          <t>16 (commerciali)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2.266.667</t>
+          <t>1.045.000</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -12122,29 +12122,29 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://legecam.cm/wp-content/uploads/2024/12/Liste-des-mediateurs-references-au-CMAG.pdf</t>
+          <t>https://ncac.org.kh/en/services/mediation/list-of-mediators/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Camerun</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>oltre 2.400 (mediatori+arbitri)</t>
+          <t>12 (lista CMAG dic. 2024)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15.938</t>
+          <t>2.266.667</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -12154,189 +12154,189 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>https://mediators.ca/our-adr-partners</t>
+          <t>https://legecam.cm/wp-content/uploads/2024/12/Liste-des-mediateurs-references-au-CMAG.pdf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Cina</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>3.176.000 mediatori popolari</t>
+          <t>oltre 2.400 (mediatori+arbitri)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>15.938</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://www.moj.gov.cn/</t>
+          <t>https://mediators.ca/our-adr-partners</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cina</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>3.680–6.743</t>
+          <t>3.176.000 mediatori popolari</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2020-2023</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>10.254</t>
+          <t>445</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://www.sicaac.gov.co/</t>
+          <t>https://www.moj.gov.cn/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Congo</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>52 (arbitri+mediatori, dato combinato)</t>
+          <t>3.680–6.743</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2020-2023</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>10.254</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>dato sub-nazionale/parziale</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>http://unicongo.cg/2021/11/J-ECO-10</t>
+          <t>https://www.sicaac.gov.co/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Corea del Sud</t>
+          <t>Congo</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>circa 5.000 (conciliatori giudiziari)</t>
+          <t>52 (arbitri+mediatori, dato combinato)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>10.348</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>http://www.cbinews.co.kr/news/articleView.html?idxno=20699</t>
+          <t>http://unicongo.cg/2021/11/J-ECO-10</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Costa d'Avorio</t>
+          <t>Corea del Sud</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>16-21 (CACI)</t>
+          <t>circa 5.000 (conciliatori giudiziari)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1.690.625</t>
+          <t>10.348</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>https://news.abidjan.net/articles/726030</t>
+          <t>http://www.cbinews.co.kr/news/articleView.html?idxno=20699</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Costa d'Avorio</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16-21 (CACI)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1.119.000</t>
+          <t>1.690.625</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -12346,29 +12346,29 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>http://www.cubadebate.cu/noticias/2025/01/16/toman-posesion-arbitros-y-mediadores-de-la-corte-cubana-de-arbitraje-comercial-internacional/</t>
+          <t>https://news.abidjan.net/articles/726030</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Dominica</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>5.143</t>
+          <t>1.119.000</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -12378,29 +12378,29 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://www.eccourts.org/court-connected-mediation</t>
+          <t>http://www.cubadebate.cu/noticias/2025/01/16/toman-posesion-arbitros-y-mediadores-de-la-corte-cubana-de-arbitraje-comercial-internacional/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Dominica</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>3.525</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>5.050</t>
+          <t>5.143</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -12410,29 +12410,29 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://www.funcionjudicial.gob.ec/</t>
+          <t>https://www.eccourts.org/court-connected-mediation</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Egitto</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>circa 80 (panel CRCICA)</t>
+          <t>3.525</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1.303.750</t>
+          <t>5.050</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -12442,29 +12442,29 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>https://crcica.org/mediation/panel-of-mediators/</t>
+          <t>https://www.funcionjudicial.gob.ec/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>El Salvador</t>
+          <t>Egitto</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>circa 80 (panel CRCICA)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>30.905</t>
+          <t>1.303.750</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -12474,93 +12474,93 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://www.pgr.gob.sv/procuraduria-especializada-de-mediacion-y-conciliacion/</t>
+          <t>https://crcica.org/mediation/panel-of-mediators/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Emirati Arabi Uniti</t>
+          <t>El Salvador</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>58+ (solo Abu Dhabi ADJD)</t>
+          <t>210</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>30.905</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>dato sub-nazionale/parziale</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>https://www.adjd.gov.ae/</t>
+          <t>https://www.pgr.gob.sv/procuraduria-especializada-de-mediacion-y-conciliacion/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Figi</t>
+          <t>Emirati Arabi Uniti</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>circa 50 (Fiji Mediation Centre)</t>
+          <t>58+ (solo Abu Dhabi ADJD)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>18.000</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://fijimediation.org/team-of-experts/</t>
+          <t>https://www.adjd.gov.ae/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Filippine</t>
+          <t>Figi</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>oltre 400 (PHILJA, dato datato)</t>
+          <t>circa 50 (Fiji Mediation Centre)</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>277.625</t>
+          <t>18.000</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -12570,29 +12570,29 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>https://philja.judiciary.gov.ph/</t>
+          <t>https://fijimediation.org/team-of-experts/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Filippine</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>circa 30 (IIMAC)</t>
+          <t>oltre 400 (PHILJA, dato datato)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>76.667</t>
+          <t>277.625</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -12602,29 +12602,29 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://gabonactu.com/blog/2023/12/25/dix-mediateurs-daffaires-recoivent-des-certificats-de-liimac/</t>
+          <t>https://philja.judiciary.gov.ph/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>circa 18 (Judiciary CC-ADR)</t>
+          <t>circa 30 (IIMAC)</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>138.333</t>
+          <t>76.667</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -12634,19 +12634,19 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>https://judiciary.gov.gm/court-connected</t>
+          <t>https://gabonactu.com/blog/2023/12/25/dix-mediateurs-daffaires-recoivent-des-certificats-de-liimac/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>circa 170</t>
+          <t>circa 18 (Judiciary CC-ADR)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>21.824</t>
+          <t>138.333</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -12666,29 +12666,29 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://mediators.ge/</t>
+          <t>https://judiciary.gov.gm/court-connected</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>336 (rete Court-Connected ADR)</t>
+          <t>circa 170</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>92.470</t>
+          <t>21.824</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -12698,29 +12698,29 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>https://gna.org.gh/2026/03/chief-justice-launches-adr-week-in-sunyani/</t>
+          <t>https://mediators.ge/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Giamaica</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>336 (rete Court-Connected ADR)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>37.237</t>
+          <t>92.470</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -12730,93 +12730,93 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://www.disputeresolutionfoundation.org/</t>
+          <t>https://gna.org.gh/2026/03/chief-justice-launches-adr-week-in-sunyani/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Giappone</t>
+          <t>Giamaica</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>19.212 (comitati di conciliazione, chotei-in)</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>6.543</t>
+          <t>37.237</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>https://www.choutei.jp/about/chouteiin/index.html</t>
+          <t>https://www.disputeresolutionfoundation.org/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Giappone</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>circa 100 (Unidad RAC OJ)</t>
+          <t>19.212 (comitati di conciliazione, chotei-in)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>176.000</t>
+          <t>6.543</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>http://asies.org.gt/pdf/201310_diagnostico_centros_de_mediacion_rac_daj.pdf</t>
+          <t>https://www.choutei.jp/about/chouteiin/index.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>circa 1.900 (HKMAAL)</t>
+          <t>circa 100 (Unidad RAC OJ)</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3.937</t>
+          <t>176.000</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -12826,147 +12826,147 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>https://www.hkmaal.org.hk/</t>
+          <t>http://asies.org.gt/pdf/201310_diagnostico_centros_de_mediacion_rac_daj.pdf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>circa 20.000 (formati, MCPC/NALSA)</t>
+          <t>oltre 400 (mediatori comunitari, 18 CRECs)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>69.650</t>
+          <t>25.700</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>https://www.livelaw.in/articles/mediation-for-the-nation-lessons-learnt-535455</t>
+          <t>https://www.undp.org/es/honduras/noticias/fortalecen-18-centros-de-resolucion-extrajudicial-de-conflictos-nivel-nacional</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>oltre 2.000 (dato parziale)</t>
+          <t>circa 1.900 (HKMAAL)</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>3.937</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>dato sub-nazionale/parziale</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>https://www.hukumonline.com/berita/a/lt62ff0e1b4d1d1/</t>
+          <t>https://www.hkmaal.org.hk/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>circa 16.000 (Consigli risoluzione controversie)</t>
+          <t>circa 20.000 (formati, MCPC/NALSA)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>5.495</t>
+          <t>69.650</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://mehrnews.com/news/6308238/</t>
+          <t>https://www.livelaw.in/articles/mediation-for-the-nation-lessons-learnt-535455</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Islanda</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>58 (Sátt)</t>
+          <t>oltre 2.000 (dato parziale)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>6.414</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>https://www.satt.is/team</t>
+          <t>https://www.hukumonline.com/berita/a/lt62ff0e1b4d1d1/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Israele</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>circa 300 (lista giudiziaria)</t>
+          <t>circa 16.000 (Consigli risoluzione controversie)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -12976,39 +12976,39 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>31.500</t>
+          <t>5.495</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>https://www.gov.il/he/pages/mediation_department</t>
+          <t>https://mehrnews.com/news/6308238/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Kazakistan</t>
+          <t>Islanda</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>371 professionali (+4.465 comunitari)</t>
+          <t>58 (Sátt)</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>51.213</t>
+          <t>6.414</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -13018,29 +13018,29 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>https://mediator.kz/reestr</t>
+          <t>https://www.satt.is/team</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Israele</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>circa 900 attivi</t>
+          <t>circa 300 (lista giudiziaria)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>2023-2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>58.900</t>
+          <t>31.500</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -13050,29 +13050,29 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>https://judiciary.go.ke/list-of-accredited-mediators/</t>
+          <t>https://www.gov.il/he/pages/mediation_department</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Kirghizistan</t>
+          <t>Kazakistan</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>371 professionali (+4.465 comunitari)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>24.686</t>
+          <t>51.213</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -13082,29 +13082,29 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>https://mediator.kg/mediators/</t>
+          <t>https://mediator.kz/reestr</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Kosovo</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>circa 900 attivi</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2023-2025</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>9.471</t>
+          <t>58.900</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -13114,29 +13114,29 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>https://ndermjetesimi.com/en/historiku/</t>
+          <t>https://judiciary.go.ke/list-of-accredited-mediators/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Liechtenstein</t>
+          <t>Kirghizistan</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>5 (Amt für Justiz)</t>
+          <t>271</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>7.800</t>
+          <t>24.686</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -13146,29 +13146,29 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>https://www.llv.li/serviceportal2/amtsstellen/amt-fuer-justiz/mediation/liste-der-eingetragenen-mediatoren.pdf</t>
+          <t>https://mediator.kg/mediators/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Macedonia</t>
+          <t>Kosovo</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>45 (Camera dei mediatori)</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>46.000</t>
+          <t>9.471</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -13178,29 +13178,29 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>https://www.kmrsm.org.mk/medijatori/</t>
+          <t>https://ndermjetesimi.com/en/historiku/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Macedonia del Nord</t>
+          <t>Liechtenstein</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>circa 45 (Camera KMRSM)</t>
+          <t>5 (Amt für Justiz)</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>46.000</t>
+          <t>7.800</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -13210,29 +13210,29 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>https://www.kmrsm.org.mk/medijatori/</t>
+          <t>https://www.llv.li/serviceportal2/amtsstellen/amt-fuer-justiz/mediation/liste-der-eingetragenen-mediatoren.pdf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Malesia</t>
+          <t>Macedonia</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>113 (panel MIMC)</t>
+          <t>45 (Camera dei mediatori)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>297.080</t>
+          <t>46.000</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -13242,29 +13242,29 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>https://www.mimc.org.my/list-of-accredited-mediators/</t>
+          <t>https://www.kmrsm.org.mk/medijatori/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Marocco</t>
+          <t>Macedonia del Nord</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>circa 50 attivi (oltre 200 formati)</t>
+          <t>circa 45 (Camera KMRSM)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>741.600</t>
+          <t>46.000</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -13274,19 +13274,19 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfcim.org/une-nouvelle-loi-encadrant-le-processus-de-mediation/</t>
+          <t>https://www.kmrsm.org.mk/medijatori/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Mauritania</t>
+          <t>Malesia</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>16 (CIMAM)</t>
+          <t>113 (panel MIMC)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>288.750</t>
+          <t>297.080</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -13306,61 +13306,61 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>https://cimam.net/index.php/fr/services-3/mediation/liste-des-mediateurs</t>
+          <t>https://www.mimc.org.my/list-of-accredited-mediators/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Messico</t>
+          <t>Marocco</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>649 (solo Città del Messico)</t>
+          <t>circa 50 attivi (oltre 200 formati)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>741.600</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>dato sub-nazionale/parziale</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>https://www.poderjudicialcdmx.gob.mx/cja/mediacion-privada-2/</t>
+          <t>https://www.cfcim.org/une-nouvelle-loi-encadrant-le-processus-de-mediation/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Mauritania</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>16 (CIMAM)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>2.682</t>
+          <t>288.750</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -13370,61 +13370,61 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>https://mediere.gov.md/sites/default/files/document/attachments/registrul_atestatelor_mediatorilor_2.pdf</t>
+          <t>https://cimam.net/index.php/fr/services-3/mediation/liste-des-mediateurs</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Messico</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>circa 400</t>
+          <t>649 (solo Città del Messico)</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>8.375</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>https://www.judcouncil.mn/</t>
+          <t>https://www.poderjudicialcdmx.gob.mx/cja/mediacion-privada-2/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>977</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>2.650</t>
+          <t>2.682</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -13434,29 +13434,29 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>https://www.cazrs.me/</t>
+          <t>https://mediere.gov.md/sites/default/files/document/attachments/registrul_atestatelor_mediatorilor_2.pdf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Mozambico</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>52 (CACM)</t>
+          <t>circa 400</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>616.923</t>
+          <t>8.375</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -13466,29 +13466,29 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>https://www.cacm.org.mz/?page_id=4379</t>
+          <t>https://www.judcouncil.mn/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>2.054 (Mediation Council)</t>
+          <t>234</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>14.620</t>
+          <t>2.650</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -13498,29 +13498,29 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>https://mediationcouncil.gov.np/pages/view/melmilap_karta</t>
+          <t>https://www.cazrs.me/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Nicaragua</t>
+          <t>Mozambico</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>circa 216 (52 centri DIRAC)</t>
+          <t>52 (CACM)</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>31.713</t>
+          <t>616.923</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -13530,29 +13530,29 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>https://www.poderjudicial.gob.ni/dirac22/centros_Activos.pdf</t>
+          <t>https://www.cacm.org.mz/?page_id=4379</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Norvegia</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>circa 550 (konfliktråd) + ~65 familiari</t>
+          <t>2.054 (Mediation Council)</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>9.836</t>
+          <t>14.620</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -13562,29 +13562,29 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>https://konfliktraadet.no/en/about-us/</t>
+          <t>https://mediationcouncil.gov.np/pages/view/melmilap_karta</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Nuova Zelanda</t>
+          <t>Nicaragua</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>oltre 1.000 (membri AMINZ, incl. arbitri)</t>
+          <t>circa 216 (52 centri DIRAC)</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>5.120</t>
+          <t>31.713</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -13594,29 +13594,29 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>https://www.aminz.org.nz/about-us</t>
+          <t>https://www.poderjudicial.gob.ni/dirac22/centros_Activos.pdf</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Norvegia</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>2 (OCAC)</t>
+          <t>circa 550 (konfliktråd) + ~65 familiari</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>2.260.000</t>
+          <t>9.836</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -13626,61 +13626,61 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>https://omanarbitration.om/ar/</t>
+          <t>https://konfliktraadet.no/en/about-us/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Nuova Zelanda</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>circa 114 (solo centro MICADR)</t>
+          <t>oltre 1.000 (membri AMINZ, incl. arbitri)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>5.120</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>dato sub-nazionale/parziale</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>https://www.micadr.com/accredited-mediator-2/</t>
+          <t>https://www.aminz.org.nz/about-us</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>circa 1.414 generali (+625 comunitari)</t>
+          <t>2 (OCAC)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>3.098</t>
+          <t>2.260.000</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -13690,61 +13690,61 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>https://www.datosabiertos.gob.pa/dataset/mingob-drac-registro-de-mediadores-y-conciliadores-del-mes-febrero-2019</t>
+          <t>https://omanarbitration.om/ar/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>circa 114 (solo centro MICADR)</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>113.559</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>https://www.pj.gov.py/contenido/150-direccion-de-mediacion/1198</t>
+          <t>https://www.micadr.com/accredited-mediator-2/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Perù</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>circa 58.738 conciliatori extragiudiziali</t>
+          <t>circa 1.414 generali (+625 comunitari)</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>3.098</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -13754,29 +13754,29 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>https://laley.pe/art/6527/existen-mas-de-52-mil-conciliadores-extrajudiciales-a-nivel-nacional</t>
+          <t>https://www.datosabiertos.gob.pa/dataset/mingob-drac-registro-de-mediadores-y-conciliadores-del-mes-febrero-2019</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>6 (panel QICDRC)</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>448.333</t>
+          <t>113.559</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -13786,29 +13786,29 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>https://www.qicdrc.gov.qa/services/mediation</t>
+          <t>https://www.pj.gov.py/contenido/150-direccion-de-mediacion/1198</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Repubblica Dominicana</t>
+          <t>Perù</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>circa 400 (formati, Poder Judicial)</t>
+          <t>circa 58.738 conciliatori extragiudiziali</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>27.800</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -13818,157 +13818,157 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>https://poderjudicial.gob.do/</t>
+          <t>https://laley.pe/art/6527/existen-mas-de-52-mil-conciliadores-extrajudiciales-a-nivel-nacional</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Ruanda</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>circa 30.000 Abunzi</t>
+          <t>6 (panel QICDRC)</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>448.333</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>https://weinsteininternational.org/</t>
+          <t>https://www.qicdrc.gov.qa/services/mediation</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Repubblica Dominicana</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>oltre 100 (unica SRO registrata)</t>
+          <t>circa 400 (formati, Poder Judicial)</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>27.800</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>dato sub-nazionale/parziale</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>https://www.all-sro.ru/register/sromed/</t>
+          <t>https://poderjudicial.gob.do/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Samoa</t>
+          <t>Ruanda</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>circa 47 (AMSA)</t>
+          <t>circa 30.000 Abunzi</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>4.681</t>
+          <t>449</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>https://www.samoaobserver.ws/en/21_12_2017/local/28089/Twenty-four-Mediators-graduate.htm</t>
+          <t>https://weinsteininternational.org/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Santa Lucia</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>circa 41</t>
+          <t>oltre 100 (unica SRO registrata)</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>4.390</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/item/global-legal-monitor/2017-06-12/saint-lucia-awareness-campaign-on-mediation-launched/</t>
+          <t>https://www.all-sro.ru/register/sromed/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Samoa</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>29 (CAMC Dakar)</t>
+          <t>circa 47 (AMSA)</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>582.069</t>
+          <t>4.681</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -13978,29 +13978,29 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>https://arbitrage-senegal.com/liste-des-mediateurs/</t>
+          <t>https://www.samoaobserver.ws/en/21_12_2017/local/28089/Twenty-four-Mediators-graduate.htm</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Santa Lucia</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>oltre 1.100</t>
+          <t>circa 41</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>6.209</t>
+          <t>4.390</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -14010,29 +14010,29 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>https://mpravde.gov.rs/registar-posrednika</t>
+          <t>https://www.loc.gov/item/global-legal-monitor/2017-06-12/saint-lucia-awareness-campaign-on-mediation-launched/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>oltre 500 (SIMI)</t>
+          <t>29 (CAMC Dakar)</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>10.900</t>
+          <t>582.069</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -14042,51 +14042,51 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>https://www.simi.org.sg/</t>
+          <t>https://arbitrage-senegal.com/liste-des-mediateurs/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>oltre 8.600</t>
+          <t>oltre 1.100</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>2.577</t>
+          <t>6.209</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>https://mediation.gov.lk/en/</t>
+          <t>https://mpravde.gov.rs/registar-posrednika</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Stati Uniti (Florida)</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>5.674 (solo Florida)</t>
+          <t>oltre 500 (SIMI)</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -14096,103 +14096,103 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>3.839</t>
+          <t>10.900</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>dato sub-nazionale/parziale</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>https://www.flcourts.gov/Resources-Services/Alternative-Dispute-Resolution/</t>
+          <t>https://www.simi.org.sg/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Sudafrica</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>233 (court-annexed, DOJ)</t>
+          <t>oltre 8.600</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>254.893</t>
+          <t>2.577</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>https://www.justice.gov.za/mediation/mediation.html</t>
+          <t>https://mediation.gov.lk/en/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Suriname</t>
+          <t>Stati Uniti (Florida)</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>circa 8 (prima coorte civile)</t>
+          <t>5.674 (solo Florida)</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>76.250</t>
+          <t>3.839</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>https://dwtonline.com/eerste-lichting-gecertificeerde-mediators-klaar-voor-inzet-in-suriname/</t>
+          <t>https://www.flcourts.gov/Resources-Services/Alternative-Dispute-Resolution/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Svizzera</t>
+          <t>Sudafrica</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>oltre 1.500 (FSM); ~200 SKWM</t>
+          <t>233 (court-annexed, DOJ)</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>5.800</t>
+          <t>254.893</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -14202,51 +14202,51 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>https://www.mediation-ch.org/</t>
+          <t>https://www.justice.gov.za/mediation/mediation.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Suriname</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>circa 4.054 (conciliatori township)</t>
+          <t>circa 8 (prima coorte civile)</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>5.814</t>
+          <t>76.250</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>mediazione popolare/comunitaria</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.tw/dataset/13947</t>
+          <t>https://dwtonline.com/eerste-lichting-gecertificeerde-mediators-klaar-voor-inzet-in-suriname/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Svizzera</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>7 (Comitato CATO)</t>
+          <t>oltre 1.500 (FSM); ~200 SKWM</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -14256,7 +14256,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1.211.429</t>
+          <t>5.800</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -14266,51 +14266,51 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>https://cato.tg/</t>
+          <t>https://www.mediation-ch.org/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Trinidad e Tobago</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>9 (roster DRC)</t>
+          <t>circa 4.054 (conciliatori township)</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>5.814</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>dato sub-nazionale/parziale</t>
+          <t>mediazione popolare/comunitaria</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>https://disputeresolutioncentre.org.tt/mediators-2/</t>
+          <t>https://data.gov.tw/dataset/13947</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11 (mediatori bancari)</t>
+          <t>7 (Comitato CATO)</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1.114.545</t>
+          <t>1.211.429</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -14330,19 +14330,19 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>https://www.cbf.org.tn/contacts-des-mediateurs-2/</t>
+          <t>https://cato.tg/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Turchia</t>
+          <t>Trinidad e Tobago</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>circa 45.154</t>
+          <t>9 (roster DRC)</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -14352,39 +14352,39 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>1.878</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>https://adb.adalet.gov.tr/</t>
+          <t>https://disputeresolutioncentre.org.tt/mediators-2/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Tuvalu</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>3 (Office People's Lawyer)</t>
+          <t>11 (mediatori bancari)</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>3.667</t>
+          <t>1.114.545</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -14394,19 +14394,19 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>https://disputescentre.com.au/mediation-in-the-south-pacific-islands/</t>
+          <t>https://www.cbf.org.tn/contacts-des-mediateurs-2/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Ucraina</t>
+          <t>Turchia</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>circa 160 (NAMU)</t>
+          <t>circa 45.154</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -14416,7 +14416,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>273.688</t>
+          <t>1.878</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -14426,29 +14426,29 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>http://namu.com.ua/ua/members/</t>
+          <t>https://adb.adalet.gov.tr/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Tuvalu</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>3 (Office People's Lawyer)</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>645.775</t>
+          <t>3.667</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -14458,29 +14458,29 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>https://judiciary.go.ug/</t>
+          <t>https://disputescentre.com.au/mediation-in-the-south-pacific-islands/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Ucraina</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>circa 30 (Centri PJ)</t>
+          <t>circa 160 (NAMU)</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>114.333</t>
+          <t>273.688</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -14490,29 +14490,29 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>https://www.poderjudicial.gub.uy/institucional/centros-de-mediacion.html</t>
+          <t>http://namu.com.ua/ua/members/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>circa 1.900 (+3.000 formati)</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>18.379</t>
+          <t>645.775</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -14522,29 +14522,29 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>https://www.adliya.uz/</t>
+          <t>https://judiciary.go.ug/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>343 (mediatori commerciali)</t>
+          <t>circa 30 (Centri PJ)</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>284.169</t>
+          <t>114.333</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -14554,53 +14554,117 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>https://tapchicongthuong.vn/phap-luat-ve-hoa-giai-thuong-mai-tu-thuc-tien-thanh-pho-ho-chi-minh-thuc-trang-va-giai-phap-103581.htm</t>
+          <t>https://www.poderjudicial.gub.uy/institucional/centros-de-mediacion.html</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>circa 1.900 (+3.000 formati)</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>18.379</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adliya.uz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>343 (mediatori commerciali)</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>284.169</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>https://tapchicongthuong.vn/phap-luat-ve-hoa-giai-thuong-mai-tu-thuc-tien-thanh-pho-ho-chi-minh-thuc-trang-va-giai-phap-103581.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
           <t>Zambia</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>102.474</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>registro professionale</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>https://judiciaryzambia.com/mediation-in-zambia-and-statistics/</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="72" customHeight="1">
-      <c r="A101" s="4" t="inlineStr">
+    <row r="103" ht="72" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>Conteggio «registro per registro» dei mediatori fuori dall'UE/UK, consultando ciascun registro ufficiale nazionale nella lingua ufficiale del luogo (ricerca luglio 2026). La densità è calcolata sulla popolazione nazionale. Le categorie «mediazione popolare/comunitaria» (Cina, Ruanda, Sri Lanka, Taiwan) e «dato sub-nazionale/parziale» (USA-Florida, Brasile) NON sono omogenee con i registri professionali e non vanno sommate. Per i Paesi non elencati non risulta pubblicato un conteggio ufficiale: N/D.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F100"/>
+  <autoFilter ref="A1:F102"/>
   <mergeCells count="1">
-    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A103:F103"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/download/ricerca-mondiale-mediazione-tabelle.xlsx
+++ b/download/ricerca-mondiale-mediazione-tabelle.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Mediazioni per Paese'!$A$1:$D$196</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2-Mediatori e registri'!$A$1:$E$196</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4-Mediatori extra-UE'!$A$1:$F$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4-Mediatori extra-UE'!$A$1:$F$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9589,12 +9589,12 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>27 (panel TIArb, arbitri+mediatori) (2026) [dato parziale/sub-nazionale]</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>mediareinformati.it — registri</t>
+          <t>Registro ufficiale nazionale (ricerca in lingua locale) — https://www.tiarb.or.tz/tiarb/panel/member</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -14305,44 +14305,44 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>7 (Comitato CATO)</t>
+          <t>27 (panel TIArb, arbitri+mediatori)</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1.211.429</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>https://cato.tg/</t>
+          <t>https://www.tiarb.or.tz/tiarb/panel/member</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Trinidad e Tobago</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>9 (roster DRC)</t>
+          <t>7 (Comitato CATO)</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -14352,29 +14352,29 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>1.211.429</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>dato sub-nazionale/parziale</t>
+          <t>registro professionale</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>https://disputeresolutioncentre.org.tt/mediators-2/</t>
+          <t>https://cato.tg/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Trinidad e Tobago</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>11 (mediatori bancari)</t>
+          <t>9 (roster DRC)</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -14384,29 +14384,29 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>1.114.545</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>registro professionale</t>
+          <t>dato sub-nazionale/parziale</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>https://www.cbf.org.tn/contacts-des-mediateurs-2/</t>
+          <t>https://disputeresolutioncentre.org.tt/mediators-2/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Turchia</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>circa 45.154</t>
+          <t>11 (mediatori bancari)</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -14416,7 +14416,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>1.878</t>
+          <t>1.114.545</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -14426,29 +14426,29 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>https://adb.adalet.gov.tr/</t>
+          <t>https://www.cbf.org.tn/contacts-des-mediateurs-2/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Tuvalu</t>
+          <t>Turchia</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>3 (Office People's Lawyer)</t>
+          <t>circa 45.154</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>3.667</t>
+          <t>1.878</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -14458,29 +14458,29 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>https://disputescentre.com.au/mediation-in-the-south-pacific-islands/</t>
+          <t>https://adb.adalet.gov.tr/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Ucraina</t>
+          <t>Tuvalu</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>circa 160 (NAMU)</t>
+          <t>3 (Office People's Lawyer)</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>273.688</t>
+          <t>3.667</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -14490,19 +14490,19 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>http://namu.com.ua/ua/members/</t>
+          <t>https://disputescentre.com.au/mediation-in-the-south-pacific-islands/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Ucraina</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>circa 160 (NAMU)</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>645.775</t>
+          <t>273.688</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -14522,29 +14522,29 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>https://judiciary.go.ug/</t>
+          <t>http://namu.com.ua/ua/members/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>circa 30 (Centri PJ)</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>114.333</t>
+          <t>645.775</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -14554,29 +14554,29 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>https://www.poderjudicial.gub.uy/institucional/centros-de-mediacion.html</t>
+          <t>https://judiciary.go.ug/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>circa 1.900 (+3.000 formati)</t>
+          <t>circa 30 (Centri PJ)</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>18.379</t>
+          <t>114.333</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -14586,29 +14586,29 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>https://www.adliya.uz/</t>
+          <t>https://www.poderjudicial.gub.uy/institucional/centros-de-mediacion.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>343 (mediatori commerciali)</t>
+          <t>circa 1.900 (+3.000 formati)</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>284.169</t>
+          <t>18.379</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -14618,53 +14618,85 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>https://tapchicongthuong.vn/phap-luat-ve-hoa-giai-thuong-mai-tu-thuc-tien-thanh-pho-ho-chi-minh-thuc-trang-va-giai-phap-103581.htm</t>
+          <t>https://www.adliya.uz/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>343 (mediatori commerciali)</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>284.169</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>https://tapchicongthuong.vn/phap-luat-ve-hoa-giai-thuong-mai-tu-thuc-tien-thanh-pho-ho-chi-minh-thuc-trang-va-giai-phap-103581.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
           <t>Zambia</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>190</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>102.474</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>registro professionale</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>https://judiciaryzambia.com/mediation-in-zambia-and-statistics/</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="72" customHeight="1">
-      <c r="A103" s="4" t="inlineStr">
+    <row r="104" ht="72" customHeight="1">
+      <c r="A104" s="4" t="inlineStr">
         <is>
           <t>Conteggio «registro per registro» dei mediatori fuori dall'UE/UK, consultando ciascun registro ufficiale nazionale nella lingua ufficiale del luogo (ricerca luglio 2026). La densità è calcolata sulla popolazione nazionale. Le categorie «mediazione popolare/comunitaria» (Cina, Ruanda, Sri Lanka, Taiwan) e «dato sub-nazionale/parziale» (USA-Florida, Brasile) NON sono omogenee con i registri professionali e non vanno sommate. Per i Paesi non elencati non risulta pubblicato un conteggio ufficiale: N/D.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F102"/>
+  <autoFilter ref="A1:F103"/>
   <mergeCells count="1">
-    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="A104:F104"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/download/ricerca-mondiale-mediazione-tabelle.xlsx
+++ b/download/ricerca-mondiale-mediazione-tabelle.xlsx
@@ -11379,7 +11379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -14690,6 +14690,38 @@
       <c r="A104" s="4" t="inlineStr">
         <is>
           <t>Conteggio «registro per registro» dei mediatori fuori dall'UE/UK, consultando ciascun registro ufficiale nazionale nella lingua ufficiale del luogo (ricerca luglio 2026). La densità è calcolata sulla popolazione nazionale. Le categorie «mediazione popolare/comunitaria» (Cina, Ruanda, Sri Lanka, Taiwan) e «dato sub-nazionale/parziale» (USA-Florida, Brasile) NON sono omogenee con i registri professionali e non vanno sommate. Per i Paesi non elencati non risulta pubblicato un conteggio ufficiale: N/D.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>26 (panel Lagos Multi-Door Courthouse, Lagos State)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>8.576.923</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>dato sub-nazionale/parziale</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://lagosmultidoor.org.ng/mediators</t>
         </is>
       </c>
     </row>

--- a/download/ricerca-mondiale-mediazione-tabelle.xlsx
+++ b/download/ricerca-mondiale-mediazione-tabelle.xlsx
@@ -11379,7 +11379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -14722,6 +14722,38 @@
       <c r="F105" t="inlineStr">
         <is>
           <t>https://lagosmultidoor.org.ng/mediators</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>172 (High Court, mediatori accreditati)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>15.116</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>registro professionale</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://ejustice.jud.na/High%20Court/Mediation/Contact%20Details/COURT-ACCREDITED%20MEDIATOR%20PROFILES%202023.pdf</t>
         </is>
       </c>
     </row>
